--- a/logs/feature_importance_analysis/surge/surge_velocity_feature_importance_analysis.xlsx
+++ b/logs/feature_importance_analysis/surge/surge_velocity_feature_importance_analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/feature_importance_analysis/surge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_7631B2A9D390532603383311595ED87656CFD6A3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9737957-10EB-4CA3-896F-133D5B99518E}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="11_7631B2A9D390532603383311595ED87656CFD6A3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2B7632D-D0B5-44B8-A2BE-8B8A4751983D}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5580" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId3"/>
+    <pivotCache cacheId="8" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="253">
   <si>
     <t>date</t>
   </si>
@@ -613,6 +613,189 @@
   </si>
   <si>
     <t>Promedio de global closed R2</t>
+  </si>
+  <si>
+    <t>15/04/2026 11:23:30</t>
+  </si>
+  <si>
+    <t>04-15_11-23-30_multihead_1heads_run2_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>['sv', 'yr', 'ya']</t>
+  </si>
+  <si>
+    <t>[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+  </si>
+  <si>
+    <t>[0, 1, 2]</t>
+  </si>
+  <si>
+    <t>04-15_11-23-30_multihead_1heads_run4_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 11:23:31</t>
+  </si>
+  <si>
+    <t>04-15_11-23-31_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 11:23:35</t>
+  </si>
+  <si>
+    <t>04-15_11-23-35_multihead_1heads_run3_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 11:23:36</t>
+  </si>
+  <si>
+    <t>04-15_11-23-36_multihead_1heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 11:53:17</t>
+  </si>
+  <si>
+    <t>04-15_11-53-17_multihead_1heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 11:53:18</t>
+  </si>
+  <si>
+    <t>04-15_11-53-18_multihead_1heads_run6_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 11:53:22</t>
+  </si>
+  <si>
+    <t>04-15_11-53-22_multihead_1heads_run7_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 12:04:27</t>
+  </si>
+  <si>
+    <t>04-15_12-04-27_multihead_1heads_run8_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 12:04:29</t>
+  </si>
+  <si>
+    <t>04-15_12-04-29_multihead_1heads_run9_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 12:23:13</t>
+  </si>
+  <si>
+    <t>04-15_12-23-13_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+  </si>
+  <si>
+    <t>15/04/2026 12:37:30</t>
+  </si>
+  <si>
+    <t>04-15_12-37-30_multihead_1heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 12:37:35</t>
+  </si>
+  <si>
+    <t>04-15_12-37-35_multihead_1heads_run2_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 12:45:04</t>
+  </si>
+  <si>
+    <t>04-15_12-45-04_multihead_1heads_run3_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 12:45:22</t>
+  </si>
+  <si>
+    <t>04-15_12-45-22_multihead_1heads_run4_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 13:24:50</t>
+  </si>
+  <si>
+    <t>04-15_13-24-50_multihead_1heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 13:43:39</t>
+  </si>
+  <si>
+    <t>04-15_13-43-39_multihead_1heads_run6_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>04-15_13-43-39_multihead_1heads_run7_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 13:46:50</t>
+  </si>
+  <si>
+    <t>04-15_13-46-50_multihead_1heads_run8_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 13:47:08</t>
+  </si>
+  <si>
+    <t>04-15_13-47-08_multihead_1heads_run9_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 14:26:37</t>
+  </si>
+  <si>
+    <t>04-15_14-26-37_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+  </si>
+  <si>
+    <t>15/04/2026 14:48:23</t>
+  </si>
+  <si>
+    <t>04-15_14-48-23_multihead_1heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>04-15_14-48-23_multihead_1heads_run2_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 14:49:58</t>
+  </si>
+  <si>
+    <t>04-15_14-49-58_multihead_1heads_run3_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 14:50:05</t>
+  </si>
+  <si>
+    <t>04-15_14-50-05_multihead_1heads_run4_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 15:48:05</t>
+  </si>
+  <si>
+    <t>04-15_15-48-05_multihead_1heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 16:10:12</t>
+  </si>
+  <si>
+    <t>04-15_16-10-12_multihead_1heads_run6_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 16:10:19</t>
+  </si>
+  <si>
+    <t>04-15_16-10-19_multihead_1heads_run7_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>15/04/2026 16:17:57</t>
+  </si>
+  <si>
+    <t>04-15_16-17-57_multihead_1heads_run8_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+  </si>
+  <si>
+    <t>04-15_16-17-57_multihead_1heads_run9_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
   </si>
 </sst>
 </file>
@@ -667,7 +850,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -676,6 +859,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -683,16 +871,16 @@
   <dxfs count="3">
     <dxf>
       <border outline="0">
-        <top style="thin">
+        <bottom style="thin">
           <color auto="1"/>
-        </top>
+        </bottom>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
+        <top style="thin">
           <color auto="1"/>
-        </bottom>
+        </top>
       </border>
     </dxf>
     <dxf>
@@ -738,7 +926,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46125.603103703703" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="50" xr:uid="{A07A839D-3B62-479C-812E-08E9EA420ADF}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46128.425351851853" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="80" xr:uid="{A07A839D-3B62-479C-812E-08E9EA420ADF}">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabla1"/>
   </cacheSource>
@@ -776,12 +964,13 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="4.5" maxValue="4.5"/>
     </cacheField>
     <cacheField name="features" numFmtId="0">
-      <sharedItems count="5">
+      <sharedItems count="6">
         <s v="['sv']"/>
         <s v="['sv', 'rarad']"/>
         <s v="['sv', 'wv']"/>
         <s v="['sv', 'yr']"/>
         <s v="['sv', 'ya']"/>
+        <s v="['sv', 'yr', 'ya']"/>
       </sharedItems>
     </cacheField>
     <cacheField name="targets" numFmtId="0">
@@ -824,10 +1013,18 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="reps" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5" count="3">
+        <n v="1"/>
+        <n v="3"/>
+        <n v="5"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="map" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="3">
+        <s v="[0, -1, -1]"/>
+        <s v="[0, 1, -1]"/>
+        <s v="[0, 1, 2]"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="reorder" numFmtId="0">
       <sharedItems/>
@@ -857,10 +1054,10 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="total params" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="40" maxValue="40"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="40" maxValue="80"/>
     </cacheField>
     <cacheField name="q params" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="10" maxValue="10"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="10" maxValue="50"/>
     </cacheField>
     <cacheField name="c params" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="30" maxValue="30"/>
@@ -869,28 +1066,28 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.1497212651004199E-2" maxValue="8.1816700508253098E-2"/>
     </cacheField>
     <cacheField name="Val Global Open MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.0369143751411E-3" maxValue="9.9025373707716004E-3"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.0369143751411E-3" maxValue="1.47605000851971E-2"/>
     </cacheField>
     <cacheField name="Val Global Open R2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.86647052670128855" maxValue="0.95904912430193756"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.80096396224472111" maxValue="0.95904912430193756"/>
     </cacheField>
     <cacheField name="Val Global Closed R2" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-9.5189924362951537" maxValue="0.62790041741894442"/>
     </cacheField>
     <cacheField name="step MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.1850843120207E-3" maxValue="1.01890487906696E-2"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.1850843120207E-3" maxValue="3.0052698304400799E-2"/>
     </cacheField>
     <cacheField name="step R2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.92601433176213321" maxValue="0.97687216971278124"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.78177855341725544" maxValue="0.97687216971278124"/>
     </cacheField>
     <cacheField name="local MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.1850843120207E-3" maxValue="1.01890487906696E-2"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.1850843120207E-3" maxValue="3.0052698304400799E-2"/>
     </cacheField>
     <cacheField name="global open MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.1850843120207E-3" maxValue="1.01890487906696E-2"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.1850843120207E-3" maxValue="3.0052698304400799E-2"/>
     </cacheField>
     <cacheField name="global open R2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.92601433176213321" maxValue="0.97687216971278124"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.78177855341725544" maxValue="0.97687216971278124"/>
     </cacheField>
     <cacheField name="global closed MSE" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="5.47971120890706E-2" maxValue="0.81083226712155188"/>
@@ -905,19 +1102,19 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Surge Velocity Step MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.1850843120207E-3" maxValue="1.01890487906696E-2"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.1850843120207E-3" maxValue="3.0052698304400799E-2"/>
     </cacheField>
     <cacheField name="Surge Velocity Step R2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.92601433176213321" maxValue="0.97687216971278124"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.78177855341725544" maxValue="0.97687216971278124"/>
     </cacheField>
     <cacheField name="Surge Velocity Local MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.1850843120207E-3" maxValue="1.01890487906696E-2"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.1850843120207E-3" maxValue="3.0052698304400799E-2"/>
     </cacheField>
     <cacheField name="Surge Velocity Global open MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.1850843120207E-3" maxValue="1.01890487906696E-2"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.1850843120207E-3" maxValue="3.0052698304400799E-2"/>
     </cacheField>
     <cacheField name="Surge Velocity Global open R2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.92601433176213321" maxValue="0.97687216971278124"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.78177855341725544" maxValue="0.97687216971278124"/>
     </cacheField>
     <cacheField name="Surge Velocity Global closed MSE" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="5.47971120890706E-2" maxValue="0.81083226712155188"/>
@@ -998,7 +1195,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="50">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="80">
   <r>
     <s v="13/04/2026 10:41:49"/>
     <s v="04-13_10-41-49_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
@@ -1021,8 +1218,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, -1, -1]"/>
+    <x v="0"/>
+    <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1099,8 +1296,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, -1, -1]"/>
+    <x v="0"/>
+    <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1177,8 +1374,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, -1, -1]"/>
+    <x v="0"/>
+    <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1255,8 +1452,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, -1, -1]"/>
+    <x v="0"/>
+    <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1333,8 +1530,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, -1, -1]"/>
+    <x v="0"/>
+    <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1411,8 +1608,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, -1, -1]"/>
+    <x v="0"/>
+    <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1489,8 +1686,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, -1, -1]"/>
+    <x v="0"/>
+    <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1567,8 +1764,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, -1, -1]"/>
+    <x v="0"/>
+    <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1645,8 +1842,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, -1, -1]"/>
+    <x v="0"/>
+    <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1723,8 +1920,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, -1, -1]"/>
+    <x v="0"/>
+    <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1801,8 +1998,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1879,8 +2076,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -1957,8 +2154,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2035,8 +2232,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2113,8 +2310,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2191,8 +2388,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2269,8 +2466,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2347,8 +2544,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2425,8 +2622,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2503,8 +2700,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2581,8 +2778,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2659,8 +2856,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2737,8 +2934,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2815,8 +3012,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2893,8 +3090,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -2971,8 +3168,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3049,8 +3246,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3127,8 +3324,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3205,8 +3402,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3283,8 +3480,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3361,8 +3558,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3439,8 +3636,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3517,8 +3714,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3595,8 +3792,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3673,8 +3870,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3751,8 +3948,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3829,8 +4026,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3907,8 +4104,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -3985,8 +4182,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4063,8 +4260,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4141,8 +4338,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4219,8 +4416,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4297,8 +4494,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4375,8 +4572,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4453,8 +4650,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4531,8 +4728,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4609,8 +4806,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4687,8 +4884,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4765,8 +4962,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4843,8 +5040,8 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <n v="1"/>
-    <s v="[0, 1, -1]"/>
+    <x v="0"/>
+    <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
     <n v="4000"/>
@@ -4899,12 +5096,2511 @@
     <m/>
     <m/>
   </r>
+  <r>
+    <s v="15/04/2026 11:23:30"/>
+    <s v="04-15_11-23-30_multihead_1heads_run2_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="2"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="6.1247570711540397E-2"/>
+    <n v="4.0424484700346004E-3"/>
+    <n v="0.94549013098055645"/>
+    <n v="-7.3850505931187342"/>
+    <n v="4.1369620740715997E-3"/>
+    <n v="0.96996030642181397"/>
+    <n v="4.1369620740715997E-3"/>
+    <n v="4.1369620740715997E-3"/>
+    <n v="0.96996030642181397"/>
+    <n v="0.65507495631200974"/>
+    <n v="-3.7566911675815011"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="4.1369620740715997E-3"/>
+    <n v="0.96996030642181397"/>
+    <n v="4.1369620740715997E-3"/>
+    <n v="4.1369620740715997E-3"/>
+    <n v="0.96996030642181397"/>
+    <n v="0.65507495631200974"/>
+    <n v="-3.7566911675815011"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 11:23:30"/>
+    <s v="04-15_11-23-30_multihead_1heads_run4_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="4"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="3.60725991310369E-2"/>
+    <n v="4.0841951671264001E-3"/>
+    <n v="0.94492720308986444"/>
+    <n v="-3.0182164064127912"/>
+    <n v="4.3472762833035999E-3"/>
+    <n v="0.96843315333523783"/>
+    <n v="4.3472762833035999E-3"/>
+    <n v="4.3472762833035999E-3"/>
+    <n v="0.96843315333523783"/>
+    <n v="0.33569409361115587"/>
+    <n v="-1.437573158160723"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="4.3472762833035999E-3"/>
+    <n v="0.96843315333523783"/>
+    <n v="4.3472762833035999E-3"/>
+    <n v="4.3472762833035999E-3"/>
+    <n v="0.96843315333523783"/>
+    <n v="0.33569409361115587"/>
+    <n v="-1.437573158160723"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 11:23:31"/>
+    <s v="04-15_11-23-31_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="0"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="5.3091455853652103E-2"/>
+    <n v="4.0985837311256004E-3"/>
+    <n v="0.944733182375738"/>
+    <n v="-7.7674325107882316"/>
+    <n v="4.4061776470795998E-3"/>
+    <n v="0.96800545327720322"/>
+    <n v="4.4061776470795998E-3"/>
+    <n v="4.4061776470795998E-3"/>
+    <n v="0.96800545327720322"/>
+    <n v="0.68433739153803741"/>
+    <n v="-3.969174282437864"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="4.4061776470795998E-3"/>
+    <n v="0.96800545327720322"/>
+    <n v="4.4061776470795998E-3"/>
+    <n v="4.4061776470795998E-3"/>
+    <n v="0.96800545327720322"/>
+    <n v="0.68433739153803741"/>
+    <n v="-3.969174282437864"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 11:23:35"/>
+    <s v="04-15_11-23-35_multihead_1heads_run3_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="3"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="5.0552505402238199E-2"/>
+    <n v="4.2084595342555004E-3"/>
+    <n v="0.9432515764427456"/>
+    <n v="-6.207340750455975"/>
+    <n v="3.9393553733429003E-3"/>
+    <n v="0.97139518656637525"/>
+    <n v="3.9393553733429003E-3"/>
+    <n v="3.9393553733429003E-3"/>
+    <n v="0.97139518656637525"/>
+    <n v="0.57082450642648241"/>
+    <n v="-3.1449239690742532"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="3.9393553733429003E-3"/>
+    <n v="0.97139518656637525"/>
+    <n v="3.9393553733429003E-3"/>
+    <n v="3.9393553733429003E-3"/>
+    <n v="0.97139518656637525"/>
+    <n v="0.57082450642648241"/>
+    <n v="-3.1449239690742532"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 11:23:36"/>
+    <s v="04-15_11-23-36_multihead_1heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="1"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="6.2148257284289299E-2"/>
+    <n v="3.050433129104E-3"/>
+    <n v="0.95886683242777082"/>
+    <n v="-7.4357398203201992"/>
+    <n v="3.2189637567306001E-3"/>
+    <n v="0.97662616113946998"/>
+    <n v="3.2189637567306001E-3"/>
+    <n v="3.2189637567306001E-3"/>
+    <n v="0.97662616113946998"/>
+    <n v="0.66111337391338409"/>
+    <n v="-3.8005378867910582"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="3.2189637567306001E-3"/>
+    <n v="0.97662616113946998"/>
+    <n v="3.2189637567306001E-3"/>
+    <n v="3.2189637567306001E-3"/>
+    <n v="0.97662616113946998"/>
+    <n v="0.66111337391338409"/>
+    <n v="-3.8005378867910582"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 11:53:17"/>
+    <s v="04-15_11-53-17_multihead_1heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="5"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="3.95533877881677E-2"/>
+    <n v="3.7164289255455E-3"/>
+    <n v="0.94988629899595878"/>
+    <n v="-5.3132528797031009"/>
+    <n v="4.2173799979529003E-3"/>
+    <n v="0.9693763683173946"/>
+    <n v="4.2173799979529003E-3"/>
+    <n v="4.2173799979529003E-3"/>
+    <n v="0.9693763683173946"/>
+    <n v="0.50026063888307803"/>
+    <n v="-2.6325390545542842"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="4.2173799979529003E-3"/>
+    <n v="0.9693763683173946"/>
+    <n v="4.2173799979529003E-3"/>
+    <n v="4.2173799979529003E-3"/>
+    <n v="0.9693763683173946"/>
+    <n v="0.50026063888307803"/>
+    <n v="-2.6325390545542842"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 11:53:18"/>
+    <s v="04-15_11-53-18_multihead_1heads_run6_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="6"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="5.0483520580977097E-2"/>
+    <n v="4.2471986543504998E-3"/>
+    <n v="0.94272920383170178"/>
+    <n v="-5.2057853719577878"/>
+    <n v="4.4435389054900999E-3"/>
+    <n v="0.96773416223458475"/>
+    <n v="4.4435389054900999E-3"/>
+    <n v="4.4435389054900999E-3"/>
+    <n v="0.96773416223458475"/>
+    <n v="0.49733371918701857"/>
+    <n v="-2.6112858331750868"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="4.4435389054900999E-3"/>
+    <n v="0.96773416223458475"/>
+    <n v="4.4435389054900999E-3"/>
+    <n v="4.4435389054900999E-3"/>
+    <n v="0.96773416223458475"/>
+    <n v="0.49733371918701857"/>
+    <n v="-2.6112858331750868"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 11:53:22"/>
+    <s v="04-15_11-53-22_multihead_1heads_run7_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="7"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="5.5477863285654599E-2"/>
+    <n v="4.2613284274075998E-3"/>
+    <n v="0.94253867275027159"/>
+    <n v="-5.0318661886668279"/>
+    <n v="4.1811457747059997E-3"/>
+    <n v="0.9696394756275154"/>
+    <n v="4.1811457747059997E-3"/>
+    <n v="4.1811457747059997E-3"/>
+    <n v="0.9696394756275154"/>
+    <n v="0.48485939145384588"/>
+    <n v="-2.5207060850437331"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="4.1811457747059997E-3"/>
+    <n v="0.9696394756275154"/>
+    <n v="4.1811457747059997E-3"/>
+    <n v="4.1811457747059997E-3"/>
+    <n v="0.9696394756275154"/>
+    <n v="0.48485939145384588"/>
+    <n v="-2.5207060850437331"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 12:04:27"/>
+    <s v="04-15_12-04-27_multihead_1heads_run8_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="8"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="4.9805192983837197E-2"/>
+    <n v="3.5301510087366E-3"/>
+    <n v="0.95239813926349404"/>
+    <n v="-4.6005888065727403"/>
+    <n v="3.4863163838498002E-3"/>
+    <n v="0.97468483539072359"/>
+    <n v="3.4863163838498002E-3"/>
+    <n v="3.4863163838498002E-3"/>
+    <n v="0.97468483539072359"/>
+    <n v="0.45054352379892892"/>
+    <n v="-2.2715285168750401"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="3.4863163838498002E-3"/>
+    <n v="0.97468483539072359"/>
+    <n v="3.4863163838498002E-3"/>
+    <n v="3.4863163838498002E-3"/>
+    <n v="0.97468483539072359"/>
+    <n v="0.45054352379892892"/>
+    <n v="-2.2715285168750401"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 12:04:29"/>
+    <s v="04-15_12-04-29_multihead_1heads_run9_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="9"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="0"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="40"/>
+    <n v="10"/>
+    <n v="30"/>
+    <n v="3.2373407287250001E-2"/>
+    <n v="4.3601151301197998E-3"/>
+    <n v="0.94120659634518722"/>
+    <n v="-6.9739516564416011"/>
+    <n v="4.3187676633809997E-3"/>
+    <n v="0.96864016277633902"/>
+    <n v="4.3187676633809997E-3"/>
+    <n v="4.3187676633809997E-3"/>
+    <n v="0.96864016277633902"/>
+    <n v="0.62614548930127856"/>
+    <n v="-3.5466258324822859"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="4.3187676633809997E-3"/>
+    <n v="0.96864016277633902"/>
+    <n v="4.3187676633809997E-3"/>
+    <n v="4.3187676633809997E-3"/>
+    <n v="0.96864016277633902"/>
+    <n v="0.62614548930127856"/>
+    <n v="-3.5466258324822859"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 12:23:13"/>
+    <s v="04-15_12-23-13_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="0"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="5.24980189942734E-2"/>
+    <n v="6.7667956682833002E-3"/>
+    <n v="0.90875402660202564"/>
+    <n v="-3.979388929858604"/>
+    <n v="8.3188113449148993E-3"/>
+    <n v="0.93959467375778205"/>
+    <n v="8.3188113449148993E-3"/>
+    <n v="8.3188113449148993E-3"/>
+    <n v="0.93959467375778205"/>
+    <n v="0.39869083919171788"/>
+    <n v="-1.8950109832555251"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="8.3188113449148993E-3"/>
+    <n v="0.93959467375778205"/>
+    <n v="8.3188113449148993E-3"/>
+    <n v="8.3188113449148993E-3"/>
+    <n v="0.93959467375778205"/>
+    <n v="0.39869083919171788"/>
+    <n v="-1.8950109832555251"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 12:37:30"/>
+    <s v="04-15_12-37-30_multihead_1heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="1"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="4.7813806640621702E-2"/>
+    <n v="9.1831812317513997E-3"/>
+    <n v="0.87617059071125469"/>
+    <n v="-1.4858839294878849"/>
+    <n v="1.3639119120835101E-2"/>
+    <n v="0.90096236036724919"/>
+    <n v="1.3639119120835101E-2"/>
+    <n v="1.3639119120835101E-2"/>
+    <n v="0.90096236036724919"/>
+    <n v="0.26335297152539489"/>
+    <n v="-0.91228307774681239"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="1.3639119120835101E-2"/>
+    <n v="0.90096236036724919"/>
+    <n v="1.3639119120835101E-2"/>
+    <n v="1.3639119120835101E-2"/>
+    <n v="0.90096236036724919"/>
+    <n v="0.26335297152539489"/>
+    <n v="-0.91228307774681239"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 12:37:35"/>
+    <s v="04-15_12-37-35_multihead_1heads_run2_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="2"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="4.99795722724602E-2"/>
+    <n v="8.2549948709592993E-3"/>
+    <n v="0.88868659860287202"/>
+    <n v="-1.940912877571997"/>
+    <n v="1.8312135645938001E-2"/>
+    <n v="0.86703021837839844"/>
+    <n v="1.8312135645938001E-2"/>
+    <n v="1.8312135645938001E-2"/>
+    <n v="0.86703021837839844"/>
+    <n v="0.27078010169161187"/>
+    <n v="-0.96621364572489243"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="1.8312135645938001E-2"/>
+    <n v="0.86703021837839844"/>
+    <n v="1.8312135645938001E-2"/>
+    <n v="1.8312135645938001E-2"/>
+    <n v="0.86703021837839844"/>
+    <n v="0.27078010169161187"/>
+    <n v="-0.96621364572489243"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 12:45:04"/>
+    <s v="04-15_12-45-04_multihead_1heads_run3_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="3"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="6.54721526937459E-2"/>
+    <n v="1.25834526252532E-2"/>
+    <n v="0.83032007470238678"/>
+    <n v="-6.5130716600259E-2"/>
+    <n v="1.68929622643656E-2"/>
+    <n v="0.87733525206095164"/>
+    <n v="1.68929622643656E-2"/>
+    <n v="1.68929622643656E-2"/>
+    <n v="0.87733525206095164"/>
+    <n v="0.13966442091699999"/>
+    <n v="-1.41442761625836E-2"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="1.68929622643656E-2"/>
+    <n v="0.87733525206095164"/>
+    <n v="1.68929622643656E-2"/>
+    <n v="1.68929622643656E-2"/>
+    <n v="0.87733525206095164"/>
+    <n v="0.13966442091699999"/>
+    <n v="-1.41442761625836E-2"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 12:45:22"/>
+    <s v="04-15_12-45-22_multihead_1heads_run4_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="4"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="4.6903536905258503E-2"/>
+    <n v="7.7454084142214996E-3"/>
+    <n v="0.89555805069849237"/>
+    <n v="-3.821182903610707"/>
+    <n v="9.6868306292309005E-3"/>
+    <n v="0.92966108496143718"/>
+    <n v="9.6868306292309005E-3"/>
+    <n v="9.6868306292309005E-3"/>
+    <n v="0.92966108496143718"/>
+    <n v="0.39728849169111208"/>
+    <n v="-1.884828127223956"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="9.6868306292309005E-3"/>
+    <n v="0.92966108496143718"/>
+    <n v="9.6868306292309005E-3"/>
+    <n v="9.6868306292309005E-3"/>
+    <n v="0.92966108496143718"/>
+    <n v="0.39728849169111208"/>
+    <n v="-1.884828127223956"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 13:24:50"/>
+    <s v="04-15_13-24-50_multihead_1heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="5"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="4.1046464925833602E-2"/>
+    <n v="7.5437417070926003E-3"/>
+    <n v="0.89827739910148752"/>
+    <n v="-1.6322216513585579"/>
+    <n v="2.2185220912376201E-2"/>
+    <n v="0.83890661160540292"/>
+    <n v="2.2185220912376201E-2"/>
+    <n v="2.2185220912376201E-2"/>
+    <n v="0.83890661160540292"/>
+    <n v="0.24565052790473149"/>
+    <n v="-0.78374044853521374"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="2.2185220912376201E-2"/>
+    <n v="0.83890661160540292"/>
+    <n v="2.2185220912376201E-2"/>
+    <n v="2.2185220912376201E-2"/>
+    <n v="0.83890661160540292"/>
+    <n v="0.24565052790473149"/>
+    <n v="-0.78374044853521374"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 13:43:39"/>
+    <s v="04-15_13-43-39_multihead_1heads_run6_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="6"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="6.5220637653753702E-2"/>
+    <n v="1.30369493559134E-2"/>
+    <n v="0.82420495720063691"/>
+    <n v="-0.9619399361691624"/>
+    <n v="2.7410241160662301E-2"/>
+    <n v="0.80096620886831604"/>
+    <n v="2.7410241160662301E-2"/>
+    <n v="2.7410241160662301E-2"/>
+    <n v="0.80096620886831604"/>
+    <n v="0.19794835292275631"/>
+    <n v="-0.43736098123175737"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="2.7410241160662301E-2"/>
+    <n v="0.80096620886831604"/>
+    <n v="2.7410241160662301E-2"/>
+    <n v="2.7410241160662301E-2"/>
+    <n v="0.80096620886831604"/>
+    <n v="0.19794835292275631"/>
+    <n v="-0.43736098123175737"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 13:43:39"/>
+    <s v="04-15_13-43-39_multihead_1heads_run7_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="7"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="5.6598803148057299E-2"/>
+    <n v="7.4804008067730996E-3"/>
+    <n v="0.89913151120844048"/>
+    <n v="-1.256008985190856"/>
+    <n v="2.06104551793777E-2"/>
+    <n v="0.85034144693376768"/>
+    <n v="2.06104551793777E-2"/>
+    <n v="2.06104551793777E-2"/>
+    <n v="0.85034144693376768"/>
+    <n v="0.22361408734599789"/>
+    <n v="-0.62372739787488984"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="2.06104551793777E-2"/>
+    <n v="0.85034144693376768"/>
+    <n v="2.06104551793777E-2"/>
+    <n v="2.06104551793777E-2"/>
+    <n v="0.85034144693376768"/>
+    <n v="0.22361408734599789"/>
+    <n v="-0.62372739787488984"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 13:46:50"/>
+    <s v="04-15_13-46-50_multihead_1heads_run8_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="8"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="4.7496318898352201E-2"/>
+    <n v="7.5963683606788002E-3"/>
+    <n v="0.89756776185683773"/>
+    <n v="-3.322739076438268"/>
+    <n v="9.9895685131398994E-3"/>
+    <n v="0.92746281649672635"/>
+    <n v="9.9895685131398994E-3"/>
+    <n v="9.9895685131398994E-3"/>
+    <n v="0.92746281649672635"/>
+    <n v="0.36430719603296868"/>
+    <n v="-1.645341277298094"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="9.9895685131398994E-3"/>
+    <n v="0.92746281649672635"/>
+    <n v="9.9895685131398994E-3"/>
+    <n v="9.9895685131398994E-3"/>
+    <n v="0.92746281649672635"/>
+    <n v="0.36430719603296868"/>
+    <n v="-1.645341277298094"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 13:47:08"/>
+    <s v="04-15_13-47-08_multihead_1heads_run9_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="9"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="1"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="60"/>
+    <n v="30"/>
+    <n v="30"/>
+    <n v="6.5685582300247902E-2"/>
+    <n v="7.6725183679851004E-3"/>
+    <n v="0.89654092701778787"/>
+    <n v="-1.5200695029441931"/>
+    <n v="2.2135973223606501E-2"/>
+    <n v="0.83926421350109015"/>
+    <n v="2.2135973223606501E-2"/>
+    <n v="2.2135973223606501E-2"/>
+    <n v="0.83926421350109015"/>
+    <n v="0.2390732672655411"/>
+    <n v="-0.73598103216940558"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="2.2135973223606501E-2"/>
+    <n v="0.83926421350109015"/>
+    <n v="2.2135973223606501E-2"/>
+    <n v="2.2135973223606501E-2"/>
+    <n v="0.83926421350109015"/>
+    <n v="0.2390732672655411"/>
+    <n v="-0.73598103216940558"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 14:26:37"/>
+    <s v="04-15_14-26-37_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="0"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="5.1501777242581002E-2"/>
+    <n v="1.24343523440227E-2"/>
+    <n v="0.83233059799313081"/>
+    <n v="8.8039814292093996E-3"/>
+    <n v="2.2278997447396899E-2"/>
+    <n v="0.83822567271198056"/>
+    <n v="2.2278997447396899E-2"/>
+    <n v="2.2278997447396899E-2"/>
+    <n v="0.83822567271198056"/>
+    <n v="0.13688394625576861"/>
+    <n v="6.0455649164030999E-3"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="2.2278997447396899E-2"/>
+    <n v="0.83822567271198056"/>
+    <n v="2.2278997447396899E-2"/>
+    <n v="2.2278997447396899E-2"/>
+    <n v="0.83822567271198056"/>
+    <n v="0.13688394625576861"/>
+    <n v="6.0455649164030999E-3"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 14:48:23"/>
+    <s v="04-15_14-48-23_multihead_1heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="1"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="5.4679739548186203E-2"/>
+    <n v="9.9393408611481993E-3"/>
+    <n v="0.86597425483666102"/>
+    <n v="-0.69266200543001211"/>
+    <n v="1.73080101567431E-2"/>
+    <n v="0.87432146772257613"/>
+    <n v="1.73080101567431E-2"/>
+    <n v="1.73080101567431E-2"/>
+    <n v="0.87432146772257613"/>
+    <n v="0.20787441514176441"/>
+    <n v="-0.50943702692862858"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="1.73080101567431E-2"/>
+    <n v="0.87432146772257613"/>
+    <n v="1.73080101567431E-2"/>
+    <n v="1.73080101567431E-2"/>
+    <n v="0.87432146772257613"/>
+    <n v="0.20787441514176441"/>
+    <n v="-0.50943702692862858"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 14:48:23"/>
+    <s v="04-15_14-48-23_multihead_1heads_run2_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="2"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="5.7020440968613098E-2"/>
+    <n v="1.31941874239743E-2"/>
+    <n v="0.82208470098502717"/>
+    <n v="-0.32071081911185018"/>
+    <n v="2.51065775289862E-2"/>
+    <n v="0.81769378537584059"/>
+    <n v="2.51065775289862E-2"/>
+    <n v="2.51065775289862E-2"/>
+    <n v="0.81769378537584059"/>
+    <n v="0.1645785268841948"/>
+    <n v="-0.195052898390388"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="2.51065775289862E-2"/>
+    <n v="0.81769378537584059"/>
+    <n v="2.51065775289862E-2"/>
+    <n v="2.51065775289862E-2"/>
+    <n v="0.81769378537584059"/>
+    <n v="0.1645785268841948"/>
+    <n v="-0.195052898390388"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 14:49:58"/>
+    <s v="04-15_14-49-58_multihead_1heads_run3_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="3"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="5.1142051352913498E-2"/>
+    <n v="8.4451080866467E-3"/>
+    <n v="0.88612304174796019"/>
+    <n v="-0.7041419475331141"/>
+    <n v="1.49686682687214E-2"/>
+    <n v="0.89130811450167535"/>
+    <n v="1.49686682687214E-2"/>
+    <n v="1.49686682687214E-2"/>
+    <n v="0.89130811450167535"/>
+    <n v="0.19243431723825349"/>
+    <n v="-0.39732195274276272"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="1.49686682687214E-2"/>
+    <n v="0.89130811450167535"/>
+    <n v="1.49686682687214E-2"/>
+    <n v="1.49686682687214E-2"/>
+    <n v="0.89130811450167535"/>
+    <n v="0.19243431723825349"/>
+    <n v="-0.39732195274276272"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 14:50:05"/>
+    <s v="04-15_14-50-05_multihead_1heads_run4_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="4"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="6.6508363572216095E-2"/>
+    <n v="1.46360368095675E-2"/>
+    <n v="0.80264227104756469"/>
+    <n v="-8.3113007182631007E-3"/>
+    <n v="2.0861434471526399E-2"/>
+    <n v="0.84851901276695063"/>
+    <n v="2.0861434471526399E-2"/>
+    <n v="2.0861434471526399E-2"/>
+    <n v="0.84851901276695063"/>
+    <n v="0.14466359633640269"/>
+    <n v="-5.04447534339773E-2"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="2.0861434471526399E-2"/>
+    <n v="0.84851901276695063"/>
+    <n v="2.0861434471526399E-2"/>
+    <n v="2.0861434471526399E-2"/>
+    <n v="0.84851901276695063"/>
+    <n v="0.14466359633640269"/>
+    <n v="-5.04447534339773E-2"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 15:48:05"/>
+    <s v="04-15_15-48-05_multihead_1heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="5"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="4.9789650844667001E-2"/>
+    <n v="1.04525922434221E-2"/>
+    <n v="0.85905338353077054"/>
+    <n v="-0.53247617539709591"/>
+    <n v="2.1401248777741501E-2"/>
+    <n v="0.84459926294631382"/>
+    <n v="2.1401248777741501E-2"/>
+    <n v="2.1401248777741501E-2"/>
+    <n v="0.84459926294631382"/>
+    <n v="0.16702134953353531"/>
+    <n v="-0.21279094929299619"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="2.1401248777741501E-2"/>
+    <n v="0.84459926294631382"/>
+    <n v="2.1401248777741501E-2"/>
+    <n v="2.1401248777741501E-2"/>
+    <n v="0.84459926294631382"/>
+    <n v="0.16702134953353531"/>
+    <n v="-0.21279094929299619"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 16:10:12"/>
+    <s v="04-15_16-10-12_multihead_1heads_run6_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="6"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="4.8132765663136803E-2"/>
+    <n v="1.0911368194382501E-2"/>
+    <n v="0.85286707907160508"/>
+    <n v="-0.4776711557474051"/>
+    <n v="2.5679205936134101E-2"/>
+    <n v="0.81353576275516026"/>
+    <n v="2.5679205936134101E-2"/>
+    <n v="2.5679205936134101E-2"/>
+    <n v="0.81353576275516026"/>
+    <n v="0.1657426803656871"/>
+    <n v="-0.20350615786820289"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="2.5679205936134101E-2"/>
+    <n v="0.81353576275516026"/>
+    <n v="2.5679205936134101E-2"/>
+    <n v="2.5679205936134101E-2"/>
+    <n v="0.81353576275516026"/>
+    <n v="0.1657426803656871"/>
+    <n v="-0.20350615786820289"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 16:10:19"/>
+    <s v="04-15_16-10-19_multihead_1heads_run7_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="7"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="4.6160804613806998E-2"/>
+    <n v="7.8909617796502993E-3"/>
+    <n v="0.89359535533114898"/>
+    <n v="2.3534514511138999E-2"/>
+    <n v="1.4935907398805501E-2"/>
+    <n v="0.89154600077571156"/>
+    <n v="1.4935907398805501E-2"/>
+    <n v="1.4935907398805501E-2"/>
+    <n v="0.89154600077571156"/>
+    <n v="0.13680377698261501"/>
+    <n v="6.6276974950442999E-3"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="1.4935907398805501E-2"/>
+    <n v="0.89154600077571156"/>
+    <n v="1.4935907398805501E-2"/>
+    <n v="1.4935907398805501E-2"/>
+    <n v="0.89154600077571156"/>
+    <n v="0.13680377698261501"/>
+    <n v="6.6276974950442999E-3"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 16:17:57"/>
+    <s v="04-15_16-17-57_multihead_1heads_run8_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="8"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="6.5384725709254396E-2"/>
+    <n v="1.47605000851971E-2"/>
+    <n v="0.80096396224472111"/>
+    <n v="-0.104392051504808"/>
+    <n v="3.0052698304400799E-2"/>
+    <n v="0.78177855341725544"/>
+    <n v="3.0052698304400799E-2"/>
+    <n v="3.0052698304400799E-2"/>
+    <n v="0.78177855341725544"/>
+    <n v="0.14650355272833609"/>
+    <n v="-6.3805215826736095E-2"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="3.0052698304400799E-2"/>
+    <n v="0.78177855341725544"/>
+    <n v="3.0052698304400799E-2"/>
+    <n v="3.0052698304400799E-2"/>
+    <n v="0.78177855341725544"/>
+    <n v="0.14650355272833609"/>
+    <n v="-6.3805215826736095E-2"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <s v="15/04/2026 16:17:57"/>
+    <s v="04-15_16-17-57_multihead_1heads_run9_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl"/>
+    <x v="9"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <x v="5"/>
+    <s v="['Surge Velocity']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="custom"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'yr', 'ya'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]"/>
+    <n v="1"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <x v="2"/>
+    <x v="2"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="80"/>
+    <n v="50"/>
+    <n v="30"/>
+    <n v="5.0636944282373302E-2"/>
+    <n v="7.4605903211662E-3"/>
+    <n v="0.89939864311714668"/>
+    <n v="-1.414778424593947"/>
+    <n v="1.7238138797533199E-2"/>
+    <n v="0.87482882413121021"/>
+    <n v="1.7238138797533199E-2"/>
+    <n v="1.7238138797533199E-2"/>
+    <n v="0.87482882413121021"/>
+    <n v="0.2392214679904649"/>
+    <n v="-0.73705716104974472"/>
+    <n v="0.2"/>
+    <s v="identity"/>
+    <n v="1.7238138797533199E-2"/>
+    <n v="0.87482882413121021"/>
+    <n v="1.7238138797533199E-2"/>
+    <n v="1.7238138797533199E-2"/>
+    <n v="0.87482882413121021"/>
+    <n v="0.2392214679904649"/>
+    <n v="-0.73705716104974472"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{65928CCC-B196-44D0-BD64-09B43FDADD25}" name="TablaDinámica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A1:D7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9F19AFFE-4AF2-43E2-BC05-2E0FC2045264}" name="TablaDinámica2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="F3:H10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="76">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="7">
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="4"/>
+        <item x="5"/>
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="21"/>
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Promedio de global open R2" fld="43" subtotal="average" baseField="21" baseItem="0"/>
+    <dataField name="Promedio de global closed R2" fld="45" subtotal="average" baseField="21" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{65928CCC-B196-44D0-BD64-09B43FDADD25}" name="TablaDinámica1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:D10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="76">
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -4928,12 +7624,13 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="6">
+      <items count="7">
         <item sd="0" x="0"/>
         <item sd="0" x="3"/>
         <item sd="0" x="4"/>
         <item sd="0" x="2"/>
         <item sd="0" x="1"/>
+        <item sd="0" x="5"/>
         <item t="default" sd="0"/>
       </items>
       <autoSortScope>
@@ -4959,7 +7656,14 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -5019,9 +7723,12 @@
     <field x="7"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="6">
+  <rowItems count="7">
     <i>
       <x v="1"/>
+    </i>
+    <i>
+      <x v="5"/>
     </i>
     <i>
       <x v="3"/>
@@ -5053,6 +7760,9 @@
       <x v="2"/>
     </i>
   </colItems>
+  <pageFields count="1">
+    <pageField fld="21" item="0" hier="-1"/>
+  </pageFields>
   <dataFields count="3">
     <dataField name="Promedio de global open R2" fld="43" subtotal="average" baseField="7" baseItem="0"/>
     <dataField name="Promedio de global closed R2" fld="45" subtotal="average" baseField="7" baseItem="0"/>
@@ -5071,8 +7781,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F6F279F-ED28-48E3-9EDA-6E0BA6486494}" name="Tabla1" displayName="Tabla1" ref="A1:BX51" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A1:BX51" xr:uid="{1F6F279F-ED28-48E3-9EDA-6E0BA6486494}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F6F279F-ED28-48E3-9EDA-6E0BA6486494}" name="Tabla1" displayName="Tabla1" ref="A1:BX81" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="0" tableBorderDxfId="1">
+  <autoFilter ref="A1:BX81" xr:uid="{1F6F279F-ED28-48E3-9EDA-6E0BA6486494}"/>
   <tableColumns count="76">
     <tableColumn id="1" xr3:uid="{D03A2B02-A3B4-41A1-A575-9A48207EA8EA}" name="date"/>
     <tableColumn id="2" xr3:uid="{6AB2BAE4-3373-4E47-9030-808EF0DC8A6A}" name="model_id"/>
@@ -5440,16 +8150,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BX51"/>
+  <dimension ref="A1:BX81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.109375" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.77734375" customWidth="1"/>
+    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.44140625" customWidth="1"/>
     <col min="8" max="8" width="10.109375" customWidth="1"/>
     <col min="10" max="10" width="14.21875" customWidth="1"/>
     <col min="11" max="11" width="9.44140625" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="13" max="13" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.6640625" customWidth="1"/>
     <col min="15" max="15" width="16.109375" customWidth="1"/>
     <col min="17" max="17" width="14.33203125" customWidth="1"/>
@@ -13449,7 +16162,7 @@
         <v>-1.8521933054271811</v>
       </c>
     </row>
-    <row r="49" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:76" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>181</v>
       </c>
@@ -13613,7 +16326,7 @@
         <v>-1.9367802455327039</v>
       </c>
     </row>
-    <row r="50" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:76" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>183</v>
       </c>
@@ -13777,7 +16490,7 @@
         <v>-1.94378704674306</v>
       </c>
     </row>
-    <row r="51" spans="1:55" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:76" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>185</v>
       </c>
@@ -13940,6 +16653,5586 @@
       <c r="BC51">
         <v>-1.996226599392275</v>
       </c>
+    </row>
+    <row r="52" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C52" s="4">
+        <v>2</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F52" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G52" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J52" s="4">
+        <v>5</v>
+      </c>
+      <c r="K52" s="4">
+        <v>5</v>
+      </c>
+      <c r="L52" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N52" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O52" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P52" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q52" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="R52" s="4">
+        <v>1</v>
+      </c>
+      <c r="S52" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T52" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U52" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V52" s="4">
+        <v>1</v>
+      </c>
+      <c r="W52" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X52" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z52" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA52" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB52" s="4"/>
+      <c r="AC52" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD52" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE52" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF52" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG52" s="4">
+        <v>40</v>
+      </c>
+      <c r="AH52" s="4">
+        <v>10</v>
+      </c>
+      <c r="AI52" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ52" s="4">
+        <v>6.1247570711540397E-2</v>
+      </c>
+      <c r="AK52" s="4">
+        <v>4.0424484700346004E-3</v>
+      </c>
+      <c r="AL52" s="4">
+        <v>0.94549013098055645</v>
+      </c>
+      <c r="AM52" s="4">
+        <v>-7.3850505931187342</v>
+      </c>
+      <c r="AN52" s="4">
+        <v>4.1369620740715997E-3</v>
+      </c>
+      <c r="AO52" s="4">
+        <v>0.96996030642181397</v>
+      </c>
+      <c r="AP52" s="4">
+        <v>4.1369620740715997E-3</v>
+      </c>
+      <c r="AQ52" s="4">
+        <v>4.1369620740715997E-3</v>
+      </c>
+      <c r="AR52" s="4">
+        <v>0.96996030642181397</v>
+      </c>
+      <c r="AS52" s="4">
+        <v>0.65507495631200974</v>
+      </c>
+      <c r="AT52" s="4">
+        <v>-3.7566911675815011</v>
+      </c>
+      <c r="AU52" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV52" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW52" s="4">
+        <v>4.1369620740715997E-3</v>
+      </c>
+      <c r="AX52" s="4">
+        <v>0.96996030642181397</v>
+      </c>
+      <c r="AY52" s="4">
+        <v>4.1369620740715997E-3</v>
+      </c>
+      <c r="AZ52" s="4">
+        <v>4.1369620740715997E-3</v>
+      </c>
+      <c r="BA52" s="4">
+        <v>0.96996030642181397</v>
+      </c>
+      <c r="BB52" s="4">
+        <v>0.65507495631200974</v>
+      </c>
+      <c r="BC52" s="4">
+        <v>-3.7566911675815011</v>
+      </c>
+      <c r="BD52" s="4"/>
+      <c r="BE52" s="4"/>
+      <c r="BF52" s="4"/>
+      <c r="BG52" s="4"/>
+      <c r="BH52" s="4"/>
+      <c r="BI52" s="4"/>
+      <c r="BJ52" s="4"/>
+      <c r="BK52" s="4"/>
+      <c r="BL52" s="4"/>
+      <c r="BM52" s="4"/>
+      <c r="BN52" s="4"/>
+      <c r="BO52" s="4"/>
+      <c r="BP52" s="4"/>
+      <c r="BQ52" s="4"/>
+      <c r="BR52" s="4"/>
+      <c r="BS52" s="4"/>
+      <c r="BT52" s="4"/>
+      <c r="BU52" s="4"/>
+      <c r="BV52" s="4"/>
+      <c r="BW52" s="4"/>
+      <c r="BX52" s="4"/>
+    </row>
+    <row r="53" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C53" s="4">
+        <v>4</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F53" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G53" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J53" s="4">
+        <v>5</v>
+      </c>
+      <c r="K53" s="4">
+        <v>5</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N53" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O53" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P53" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q53" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="R53" s="4">
+        <v>1</v>
+      </c>
+      <c r="S53" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T53" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U53" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V53" s="4">
+        <v>1</v>
+      </c>
+      <c r="W53" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X53" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z53" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA53" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB53" s="4"/>
+      <c r="AC53" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD53" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE53" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF53" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG53" s="4">
+        <v>40</v>
+      </c>
+      <c r="AH53" s="4">
+        <v>10</v>
+      </c>
+      <c r="AI53" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ53" s="4">
+        <v>3.60725991310369E-2</v>
+      </c>
+      <c r="AK53" s="4">
+        <v>4.0841951671264001E-3</v>
+      </c>
+      <c r="AL53" s="4">
+        <v>0.94492720308986444</v>
+      </c>
+      <c r="AM53" s="4">
+        <v>-3.0182164064127912</v>
+      </c>
+      <c r="AN53" s="4">
+        <v>4.3472762833035999E-3</v>
+      </c>
+      <c r="AO53" s="4">
+        <v>0.96843315333523783</v>
+      </c>
+      <c r="AP53" s="4">
+        <v>4.3472762833035999E-3</v>
+      </c>
+      <c r="AQ53" s="4">
+        <v>4.3472762833035999E-3</v>
+      </c>
+      <c r="AR53" s="4">
+        <v>0.96843315333523783</v>
+      </c>
+      <c r="AS53" s="4">
+        <v>0.33569409361115587</v>
+      </c>
+      <c r="AT53" s="4">
+        <v>-1.437573158160723</v>
+      </c>
+      <c r="AU53" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV53" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW53" s="4">
+        <v>4.3472762833035999E-3</v>
+      </c>
+      <c r="AX53" s="4">
+        <v>0.96843315333523783</v>
+      </c>
+      <c r="AY53" s="4">
+        <v>4.3472762833035999E-3</v>
+      </c>
+      <c r="AZ53" s="4">
+        <v>4.3472762833035999E-3</v>
+      </c>
+      <c r="BA53" s="4">
+        <v>0.96843315333523783</v>
+      </c>
+      <c r="BB53" s="4">
+        <v>0.33569409361115587</v>
+      </c>
+      <c r="BC53" s="4">
+        <v>-1.437573158160723</v>
+      </c>
+      <c r="BD53" s="4"/>
+      <c r="BE53" s="4"/>
+      <c r="BF53" s="4"/>
+      <c r="BG53" s="4"/>
+      <c r="BH53" s="4"/>
+      <c r="BI53" s="4"/>
+      <c r="BJ53" s="4"/>
+      <c r="BK53" s="4"/>
+      <c r="BL53" s="4"/>
+      <c r="BM53" s="4"/>
+      <c r="BN53" s="4"/>
+      <c r="BO53" s="4"/>
+      <c r="BP53" s="4"/>
+      <c r="BQ53" s="4"/>
+      <c r="BR53" s="4"/>
+      <c r="BS53" s="4"/>
+      <c r="BT53" s="4"/>
+      <c r="BU53" s="4"/>
+      <c r="BV53" s="4"/>
+      <c r="BW53" s="4"/>
+      <c r="BX53" s="4"/>
+    </row>
+    <row r="54" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C54" s="4">
+        <v>0</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F54" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G54" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J54" s="4">
+        <v>5</v>
+      </c>
+      <c r="K54" s="4">
+        <v>5</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M54" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P54" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q54" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="R54" s="4">
+        <v>1</v>
+      </c>
+      <c r="S54" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T54" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U54" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V54" s="4">
+        <v>1</v>
+      </c>
+      <c r="W54" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z54" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA54" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB54" s="4"/>
+      <c r="AC54" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD54" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE54" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF54" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG54" s="4">
+        <v>40</v>
+      </c>
+      <c r="AH54" s="4">
+        <v>10</v>
+      </c>
+      <c r="AI54" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ54" s="4">
+        <v>5.3091455853652103E-2</v>
+      </c>
+      <c r="AK54" s="4">
+        <v>4.0985837311256004E-3</v>
+      </c>
+      <c r="AL54" s="4">
+        <v>0.944733182375738</v>
+      </c>
+      <c r="AM54" s="4">
+        <v>-7.7674325107882316</v>
+      </c>
+      <c r="AN54" s="4">
+        <v>4.4061776470795998E-3</v>
+      </c>
+      <c r="AO54" s="4">
+        <v>0.96800545327720322</v>
+      </c>
+      <c r="AP54" s="4">
+        <v>4.4061776470795998E-3</v>
+      </c>
+      <c r="AQ54" s="4">
+        <v>4.4061776470795998E-3</v>
+      </c>
+      <c r="AR54" s="4">
+        <v>0.96800545327720322</v>
+      </c>
+      <c r="AS54" s="4">
+        <v>0.68433739153803741</v>
+      </c>
+      <c r="AT54" s="4">
+        <v>-3.969174282437864</v>
+      </c>
+      <c r="AU54" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV54" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW54" s="4">
+        <v>4.4061776470795998E-3</v>
+      </c>
+      <c r="AX54" s="4">
+        <v>0.96800545327720322</v>
+      </c>
+      <c r="AY54" s="4">
+        <v>4.4061776470795998E-3</v>
+      </c>
+      <c r="AZ54" s="4">
+        <v>4.4061776470795998E-3</v>
+      </c>
+      <c r="BA54" s="4">
+        <v>0.96800545327720322</v>
+      </c>
+      <c r="BB54" s="4">
+        <v>0.68433739153803741</v>
+      </c>
+      <c r="BC54" s="4">
+        <v>-3.969174282437864</v>
+      </c>
+      <c r="BD54" s="4"/>
+      <c r="BE54" s="4"/>
+      <c r="BF54" s="4"/>
+      <c r="BG54" s="4"/>
+      <c r="BH54" s="4"/>
+      <c r="BI54" s="4"/>
+      <c r="BJ54" s="4"/>
+      <c r="BK54" s="4"/>
+      <c r="BL54" s="4"/>
+      <c r="BM54" s="4"/>
+      <c r="BN54" s="4"/>
+      <c r="BO54" s="4"/>
+      <c r="BP54" s="4"/>
+      <c r="BQ54" s="4"/>
+      <c r="BR54" s="4"/>
+      <c r="BS54" s="4"/>
+      <c r="BT54" s="4"/>
+      <c r="BU54" s="4"/>
+      <c r="BV54" s="4"/>
+      <c r="BW54" s="4"/>
+      <c r="BX54" s="4"/>
+    </row>
+    <row r="55" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C55" s="4">
+        <v>3</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F55" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G55" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J55" s="4">
+        <v>5</v>
+      </c>
+      <c r="K55" s="4">
+        <v>5</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M55" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P55" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q55" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="R55" s="4">
+        <v>1</v>
+      </c>
+      <c r="S55" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T55" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U55" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V55" s="4">
+        <v>1</v>
+      </c>
+      <c r="W55" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z55" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA55" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB55" s="4"/>
+      <c r="AC55" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD55" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE55" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF55" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG55" s="4">
+        <v>40</v>
+      </c>
+      <c r="AH55" s="4">
+        <v>10</v>
+      </c>
+      <c r="AI55" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ55" s="4">
+        <v>5.0552505402238199E-2</v>
+      </c>
+      <c r="AK55" s="4">
+        <v>4.2084595342555004E-3</v>
+      </c>
+      <c r="AL55" s="4">
+        <v>0.9432515764427456</v>
+      </c>
+      <c r="AM55" s="4">
+        <v>-6.207340750455975</v>
+      </c>
+      <c r="AN55" s="4">
+        <v>3.9393553733429003E-3</v>
+      </c>
+      <c r="AO55" s="4">
+        <v>0.97139518656637525</v>
+      </c>
+      <c r="AP55" s="4">
+        <v>3.9393553733429003E-3</v>
+      </c>
+      <c r="AQ55" s="4">
+        <v>3.9393553733429003E-3</v>
+      </c>
+      <c r="AR55" s="4">
+        <v>0.97139518656637525</v>
+      </c>
+      <c r="AS55" s="4">
+        <v>0.57082450642648241</v>
+      </c>
+      <c r="AT55" s="4">
+        <v>-3.1449239690742532</v>
+      </c>
+      <c r="AU55" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV55" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW55" s="4">
+        <v>3.9393553733429003E-3</v>
+      </c>
+      <c r="AX55" s="4">
+        <v>0.97139518656637525</v>
+      </c>
+      <c r="AY55" s="4">
+        <v>3.9393553733429003E-3</v>
+      </c>
+      <c r="AZ55" s="4">
+        <v>3.9393553733429003E-3</v>
+      </c>
+      <c r="BA55" s="4">
+        <v>0.97139518656637525</v>
+      </c>
+      <c r="BB55" s="4">
+        <v>0.57082450642648241</v>
+      </c>
+      <c r="BC55" s="4">
+        <v>-3.1449239690742532</v>
+      </c>
+      <c r="BD55" s="4"/>
+      <c r="BE55" s="4"/>
+      <c r="BF55" s="4"/>
+      <c r="BG55" s="4"/>
+      <c r="BH55" s="4"/>
+      <c r="BI55" s="4"/>
+      <c r="BJ55" s="4"/>
+      <c r="BK55" s="4"/>
+      <c r="BL55" s="4"/>
+      <c r="BM55" s="4"/>
+      <c r="BN55" s="4"/>
+      <c r="BO55" s="4"/>
+      <c r="BP55" s="4"/>
+      <c r="BQ55" s="4"/>
+      <c r="BR55" s="4"/>
+      <c r="BS55" s="4"/>
+      <c r="BT55" s="4"/>
+      <c r="BU55" s="4"/>
+      <c r="BV55" s="4"/>
+      <c r="BW55" s="4"/>
+      <c r="BX55" s="4"/>
+    </row>
+    <row r="56" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C56" s="4">
+        <v>1</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F56" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G56" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J56" s="4">
+        <v>5</v>
+      </c>
+      <c r="K56" s="4">
+        <v>5</v>
+      </c>
+      <c r="L56" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M56" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N56" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O56" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P56" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q56" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="R56" s="4">
+        <v>1</v>
+      </c>
+      <c r="S56" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T56" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U56" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V56" s="4">
+        <v>1</v>
+      </c>
+      <c r="W56" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X56" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y56" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z56" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA56" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB56" s="4"/>
+      <c r="AC56" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD56" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE56" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF56" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG56" s="4">
+        <v>40</v>
+      </c>
+      <c r="AH56" s="4">
+        <v>10</v>
+      </c>
+      <c r="AI56" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ56" s="4">
+        <v>6.2148257284289299E-2</v>
+      </c>
+      <c r="AK56" s="4">
+        <v>3.050433129104E-3</v>
+      </c>
+      <c r="AL56" s="4">
+        <v>0.95886683242777082</v>
+      </c>
+      <c r="AM56" s="4">
+        <v>-7.4357398203201992</v>
+      </c>
+      <c r="AN56" s="4">
+        <v>3.2189637567306001E-3</v>
+      </c>
+      <c r="AO56" s="4">
+        <v>0.97662616113946998</v>
+      </c>
+      <c r="AP56" s="4">
+        <v>3.2189637567306001E-3</v>
+      </c>
+      <c r="AQ56" s="4">
+        <v>3.2189637567306001E-3</v>
+      </c>
+      <c r="AR56" s="4">
+        <v>0.97662616113946998</v>
+      </c>
+      <c r="AS56" s="4">
+        <v>0.66111337391338409</v>
+      </c>
+      <c r="AT56" s="4">
+        <v>-3.8005378867910582</v>
+      </c>
+      <c r="AU56" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV56" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW56" s="4">
+        <v>3.2189637567306001E-3</v>
+      </c>
+      <c r="AX56" s="4">
+        <v>0.97662616113946998</v>
+      </c>
+      <c r="AY56" s="4">
+        <v>3.2189637567306001E-3</v>
+      </c>
+      <c r="AZ56" s="4">
+        <v>3.2189637567306001E-3</v>
+      </c>
+      <c r="BA56" s="4">
+        <v>0.97662616113946998</v>
+      </c>
+      <c r="BB56" s="4">
+        <v>0.66111337391338409</v>
+      </c>
+      <c r="BC56" s="4">
+        <v>-3.8005378867910582</v>
+      </c>
+      <c r="BD56" s="4"/>
+      <c r="BE56" s="4"/>
+      <c r="BF56" s="4"/>
+      <c r="BG56" s="4"/>
+      <c r="BH56" s="4"/>
+      <c r="BI56" s="4"/>
+      <c r="BJ56" s="4"/>
+      <c r="BK56" s="4"/>
+      <c r="BL56" s="4"/>
+      <c r="BM56" s="4"/>
+      <c r="BN56" s="4"/>
+      <c r="BO56" s="4"/>
+      <c r="BP56" s="4"/>
+      <c r="BQ56" s="4"/>
+      <c r="BR56" s="4"/>
+      <c r="BS56" s="4"/>
+      <c r="BT56" s="4"/>
+      <c r="BU56" s="4"/>
+      <c r="BV56" s="4"/>
+      <c r="BW56" s="4"/>
+      <c r="BX56" s="4"/>
+    </row>
+    <row r="57" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C57" s="4">
+        <v>5</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F57" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G57" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J57" s="4">
+        <v>5</v>
+      </c>
+      <c r="K57" s="4">
+        <v>5</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M57" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N57" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O57" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P57" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q57" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="R57" s="4">
+        <v>1</v>
+      </c>
+      <c r="S57" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T57" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U57" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V57" s="4">
+        <v>1</v>
+      </c>
+      <c r="W57" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X57" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z57" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA57" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB57" s="4"/>
+      <c r="AC57" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD57" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE57" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF57" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG57" s="4">
+        <v>40</v>
+      </c>
+      <c r="AH57" s="4">
+        <v>10</v>
+      </c>
+      <c r="AI57" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ57" s="4">
+        <v>3.95533877881677E-2</v>
+      </c>
+      <c r="AK57" s="4">
+        <v>3.7164289255455E-3</v>
+      </c>
+      <c r="AL57" s="4">
+        <v>0.94988629899595878</v>
+      </c>
+      <c r="AM57" s="4">
+        <v>-5.3132528797031009</v>
+      </c>
+      <c r="AN57" s="4">
+        <v>4.2173799979529003E-3</v>
+      </c>
+      <c r="AO57" s="4">
+        <v>0.9693763683173946</v>
+      </c>
+      <c r="AP57" s="4">
+        <v>4.2173799979529003E-3</v>
+      </c>
+      <c r="AQ57" s="4">
+        <v>4.2173799979529003E-3</v>
+      </c>
+      <c r="AR57" s="4">
+        <v>0.9693763683173946</v>
+      </c>
+      <c r="AS57" s="4">
+        <v>0.50026063888307803</v>
+      </c>
+      <c r="AT57" s="4">
+        <v>-2.6325390545542842</v>
+      </c>
+      <c r="AU57" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV57" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW57" s="4">
+        <v>4.2173799979529003E-3</v>
+      </c>
+      <c r="AX57" s="4">
+        <v>0.9693763683173946</v>
+      </c>
+      <c r="AY57" s="4">
+        <v>4.2173799979529003E-3</v>
+      </c>
+      <c r="AZ57" s="4">
+        <v>4.2173799979529003E-3</v>
+      </c>
+      <c r="BA57" s="4">
+        <v>0.9693763683173946</v>
+      </c>
+      <c r="BB57" s="4">
+        <v>0.50026063888307803</v>
+      </c>
+      <c r="BC57" s="4">
+        <v>-2.6325390545542842</v>
+      </c>
+      <c r="BD57" s="4"/>
+      <c r="BE57" s="4"/>
+      <c r="BF57" s="4"/>
+      <c r="BG57" s="4"/>
+      <c r="BH57" s="4"/>
+      <c r="BI57" s="4"/>
+      <c r="BJ57" s="4"/>
+      <c r="BK57" s="4"/>
+      <c r="BL57" s="4"/>
+      <c r="BM57" s="4"/>
+      <c r="BN57" s="4"/>
+      <c r="BO57" s="4"/>
+      <c r="BP57" s="4"/>
+      <c r="BQ57" s="4"/>
+      <c r="BR57" s="4"/>
+      <c r="BS57" s="4"/>
+      <c r="BT57" s="4"/>
+      <c r="BU57" s="4"/>
+      <c r="BV57" s="4"/>
+      <c r="BW57" s="4"/>
+      <c r="BX57" s="4"/>
+    </row>
+    <row r="58" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A58" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C58" s="4">
+        <v>6</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F58" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G58" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J58" s="4">
+        <v>5</v>
+      </c>
+      <c r="K58" s="4">
+        <v>5</v>
+      </c>
+      <c r="L58" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M58" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N58" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O58" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P58" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q58" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="R58" s="4">
+        <v>1</v>
+      </c>
+      <c r="S58" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T58" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U58" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V58" s="4">
+        <v>1</v>
+      </c>
+      <c r="W58" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X58" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z58" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA58" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB58" s="4"/>
+      <c r="AC58" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD58" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE58" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF58" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG58" s="4">
+        <v>40</v>
+      </c>
+      <c r="AH58" s="4">
+        <v>10</v>
+      </c>
+      <c r="AI58" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ58" s="4">
+        <v>5.0483520580977097E-2</v>
+      </c>
+      <c r="AK58" s="4">
+        <v>4.2471986543504998E-3</v>
+      </c>
+      <c r="AL58" s="4">
+        <v>0.94272920383170178</v>
+      </c>
+      <c r="AM58" s="4">
+        <v>-5.2057853719577878</v>
+      </c>
+      <c r="AN58" s="4">
+        <v>4.4435389054900999E-3</v>
+      </c>
+      <c r="AO58" s="4">
+        <v>0.96773416223458475</v>
+      </c>
+      <c r="AP58" s="4">
+        <v>4.4435389054900999E-3</v>
+      </c>
+      <c r="AQ58" s="4">
+        <v>4.4435389054900999E-3</v>
+      </c>
+      <c r="AR58" s="4">
+        <v>0.96773416223458475</v>
+      </c>
+      <c r="AS58" s="4">
+        <v>0.49733371918701857</v>
+      </c>
+      <c r="AT58" s="4">
+        <v>-2.6112858331750868</v>
+      </c>
+      <c r="AU58" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV58" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW58" s="4">
+        <v>4.4435389054900999E-3</v>
+      </c>
+      <c r="AX58" s="4">
+        <v>0.96773416223458475</v>
+      </c>
+      <c r="AY58" s="4">
+        <v>4.4435389054900999E-3</v>
+      </c>
+      <c r="AZ58" s="4">
+        <v>4.4435389054900999E-3</v>
+      </c>
+      <c r="BA58" s="4">
+        <v>0.96773416223458475</v>
+      </c>
+      <c r="BB58" s="4">
+        <v>0.49733371918701857</v>
+      </c>
+      <c r="BC58" s="4">
+        <v>-2.6112858331750868</v>
+      </c>
+      <c r="BD58" s="4"/>
+      <c r="BE58" s="4"/>
+      <c r="BF58" s="4"/>
+      <c r="BG58" s="4"/>
+      <c r="BH58" s="4"/>
+      <c r="BI58" s="4"/>
+      <c r="BJ58" s="4"/>
+      <c r="BK58" s="4"/>
+      <c r="BL58" s="4"/>
+      <c r="BM58" s="4"/>
+      <c r="BN58" s="4"/>
+      <c r="BO58" s="4"/>
+      <c r="BP58" s="4"/>
+      <c r="BQ58" s="4"/>
+      <c r="BR58" s="4"/>
+      <c r="BS58" s="4"/>
+      <c r="BT58" s="4"/>
+      <c r="BU58" s="4"/>
+      <c r="BV58" s="4"/>
+      <c r="BW58" s="4"/>
+      <c r="BX58" s="4"/>
+    </row>
+    <row r="59" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C59" s="4">
+        <v>7</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F59" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G59" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J59" s="4">
+        <v>5</v>
+      </c>
+      <c r="K59" s="4">
+        <v>5</v>
+      </c>
+      <c r="L59" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M59" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N59" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O59" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P59" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q59" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="R59" s="4">
+        <v>1</v>
+      </c>
+      <c r="S59" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T59" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U59" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V59" s="4">
+        <v>1</v>
+      </c>
+      <c r="W59" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X59" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z59" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA59" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB59" s="4"/>
+      <c r="AC59" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD59" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE59" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF59" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG59" s="4">
+        <v>40</v>
+      </c>
+      <c r="AH59" s="4">
+        <v>10</v>
+      </c>
+      <c r="AI59" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ59" s="4">
+        <v>5.5477863285654599E-2</v>
+      </c>
+      <c r="AK59" s="4">
+        <v>4.2613284274075998E-3</v>
+      </c>
+      <c r="AL59" s="4">
+        <v>0.94253867275027159</v>
+      </c>
+      <c r="AM59" s="4">
+        <v>-5.0318661886668279</v>
+      </c>
+      <c r="AN59" s="4">
+        <v>4.1811457747059997E-3</v>
+      </c>
+      <c r="AO59" s="4">
+        <v>0.9696394756275154</v>
+      </c>
+      <c r="AP59" s="4">
+        <v>4.1811457747059997E-3</v>
+      </c>
+      <c r="AQ59" s="4">
+        <v>4.1811457747059997E-3</v>
+      </c>
+      <c r="AR59" s="4">
+        <v>0.9696394756275154</v>
+      </c>
+      <c r="AS59" s="4">
+        <v>0.48485939145384588</v>
+      </c>
+      <c r="AT59" s="4">
+        <v>-2.5207060850437331</v>
+      </c>
+      <c r="AU59" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV59" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW59" s="4">
+        <v>4.1811457747059997E-3</v>
+      </c>
+      <c r="AX59" s="4">
+        <v>0.9696394756275154</v>
+      </c>
+      <c r="AY59" s="4">
+        <v>4.1811457747059997E-3</v>
+      </c>
+      <c r="AZ59" s="4">
+        <v>4.1811457747059997E-3</v>
+      </c>
+      <c r="BA59" s="4">
+        <v>0.9696394756275154</v>
+      </c>
+      <c r="BB59" s="4">
+        <v>0.48485939145384588</v>
+      </c>
+      <c r="BC59" s="4">
+        <v>-2.5207060850437331</v>
+      </c>
+      <c r="BD59" s="4"/>
+      <c r="BE59" s="4"/>
+      <c r="BF59" s="4"/>
+      <c r="BG59" s="4"/>
+      <c r="BH59" s="4"/>
+      <c r="BI59" s="4"/>
+      <c r="BJ59" s="4"/>
+      <c r="BK59" s="4"/>
+      <c r="BL59" s="4"/>
+      <c r="BM59" s="4"/>
+      <c r="BN59" s="4"/>
+      <c r="BO59" s="4"/>
+      <c r="BP59" s="4"/>
+      <c r="BQ59" s="4"/>
+      <c r="BR59" s="4"/>
+      <c r="BS59" s="4"/>
+      <c r="BT59" s="4"/>
+      <c r="BU59" s="4"/>
+      <c r="BV59" s="4"/>
+      <c r="BW59" s="4"/>
+      <c r="BX59" s="4"/>
+    </row>
+    <row r="60" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A60" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C60" s="4">
+        <v>8</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F60" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G60" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J60" s="4">
+        <v>5</v>
+      </c>
+      <c r="K60" s="4">
+        <v>5</v>
+      </c>
+      <c r="L60" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M60" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N60" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O60" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P60" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q60" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="R60" s="4">
+        <v>1</v>
+      </c>
+      <c r="S60" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T60" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U60" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V60" s="4">
+        <v>1</v>
+      </c>
+      <c r="W60" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X60" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z60" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA60" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB60" s="4"/>
+      <c r="AC60" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD60" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE60" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF60" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG60" s="4">
+        <v>40</v>
+      </c>
+      <c r="AH60" s="4">
+        <v>10</v>
+      </c>
+      <c r="AI60" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ60" s="4">
+        <v>4.9805192983837197E-2</v>
+      </c>
+      <c r="AK60" s="4">
+        <v>3.5301510087366E-3</v>
+      </c>
+      <c r="AL60" s="4">
+        <v>0.95239813926349404</v>
+      </c>
+      <c r="AM60" s="4">
+        <v>-4.6005888065727403</v>
+      </c>
+      <c r="AN60" s="4">
+        <v>3.4863163838498002E-3</v>
+      </c>
+      <c r="AO60" s="4">
+        <v>0.97468483539072359</v>
+      </c>
+      <c r="AP60" s="4">
+        <v>3.4863163838498002E-3</v>
+      </c>
+      <c r="AQ60" s="4">
+        <v>3.4863163838498002E-3</v>
+      </c>
+      <c r="AR60" s="4">
+        <v>0.97468483539072359</v>
+      </c>
+      <c r="AS60" s="4">
+        <v>0.45054352379892892</v>
+      </c>
+      <c r="AT60" s="4">
+        <v>-2.2715285168750401</v>
+      </c>
+      <c r="AU60" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV60" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW60" s="4">
+        <v>3.4863163838498002E-3</v>
+      </c>
+      <c r="AX60" s="4">
+        <v>0.97468483539072359</v>
+      </c>
+      <c r="AY60" s="4">
+        <v>3.4863163838498002E-3</v>
+      </c>
+      <c r="AZ60" s="4">
+        <v>3.4863163838498002E-3</v>
+      </c>
+      <c r="BA60" s="4">
+        <v>0.97468483539072359</v>
+      </c>
+      <c r="BB60" s="4">
+        <v>0.45054352379892892</v>
+      </c>
+      <c r="BC60" s="4">
+        <v>-2.2715285168750401</v>
+      </c>
+      <c r="BD60" s="4"/>
+      <c r="BE60" s="4"/>
+      <c r="BF60" s="4"/>
+      <c r="BG60" s="4"/>
+      <c r="BH60" s="4"/>
+      <c r="BI60" s="4"/>
+      <c r="BJ60" s="4"/>
+      <c r="BK60" s="4"/>
+      <c r="BL60" s="4"/>
+      <c r="BM60" s="4"/>
+      <c r="BN60" s="4"/>
+      <c r="BO60" s="4"/>
+      <c r="BP60" s="4"/>
+      <c r="BQ60" s="4"/>
+      <c r="BR60" s="4"/>
+      <c r="BS60" s="4"/>
+      <c r="BT60" s="4"/>
+      <c r="BU60" s="4"/>
+      <c r="BV60" s="4"/>
+      <c r="BW60" s="4"/>
+      <c r="BX60" s="4"/>
+    </row>
+    <row r="61" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C61" s="4">
+        <v>9</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F61" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G61" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J61" s="4">
+        <v>5</v>
+      </c>
+      <c r="K61" s="4">
+        <v>5</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M61" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P61" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q61" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="R61" s="4">
+        <v>1</v>
+      </c>
+      <c r="S61" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T61" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U61" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V61" s="4">
+        <v>1</v>
+      </c>
+      <c r="W61" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z61" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA61" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB61" s="4"/>
+      <c r="AC61" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD61" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE61" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF61" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG61" s="4">
+        <v>40</v>
+      </c>
+      <c r="AH61" s="4">
+        <v>10</v>
+      </c>
+      <c r="AI61" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ61" s="4">
+        <v>3.2373407287250001E-2</v>
+      </c>
+      <c r="AK61" s="4">
+        <v>4.3601151301197998E-3</v>
+      </c>
+      <c r="AL61" s="4">
+        <v>0.94120659634518722</v>
+      </c>
+      <c r="AM61" s="4">
+        <v>-6.9739516564416011</v>
+      </c>
+      <c r="AN61" s="4">
+        <v>4.3187676633809997E-3</v>
+      </c>
+      <c r="AO61" s="4">
+        <v>0.96864016277633902</v>
+      </c>
+      <c r="AP61" s="4">
+        <v>4.3187676633809997E-3</v>
+      </c>
+      <c r="AQ61" s="4">
+        <v>4.3187676633809997E-3</v>
+      </c>
+      <c r="AR61" s="4">
+        <v>0.96864016277633902</v>
+      </c>
+      <c r="AS61" s="4">
+        <v>0.62614548930127856</v>
+      </c>
+      <c r="AT61" s="4">
+        <v>-3.5466258324822859</v>
+      </c>
+      <c r="AU61" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV61" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW61" s="4">
+        <v>4.3187676633809997E-3</v>
+      </c>
+      <c r="AX61" s="4">
+        <v>0.96864016277633902</v>
+      </c>
+      <c r="AY61" s="4">
+        <v>4.3187676633809997E-3</v>
+      </c>
+      <c r="AZ61" s="4">
+        <v>4.3187676633809997E-3</v>
+      </c>
+      <c r="BA61" s="4">
+        <v>0.96864016277633902</v>
+      </c>
+      <c r="BB61" s="4">
+        <v>0.62614548930127856</v>
+      </c>
+      <c r="BC61" s="4">
+        <v>-3.5466258324822859</v>
+      </c>
+      <c r="BD61" s="4"/>
+      <c r="BE61" s="4"/>
+      <c r="BF61" s="4"/>
+      <c r="BG61" s="4"/>
+      <c r="BH61" s="4"/>
+      <c r="BI61" s="4"/>
+      <c r="BJ61" s="4"/>
+      <c r="BK61" s="4"/>
+      <c r="BL61" s="4"/>
+      <c r="BM61" s="4"/>
+      <c r="BN61" s="4"/>
+      <c r="BO61" s="4"/>
+      <c r="BP61" s="4"/>
+      <c r="BQ61" s="4"/>
+      <c r="BR61" s="4"/>
+      <c r="BS61" s="4"/>
+      <c r="BT61" s="4"/>
+      <c r="BU61" s="4"/>
+      <c r="BV61" s="4"/>
+      <c r="BW61" s="4"/>
+      <c r="BX61" s="4"/>
+    </row>
+    <row r="62" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A62" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C62" s="4">
+        <v>0</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F62" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G62" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J62" s="4">
+        <v>5</v>
+      </c>
+      <c r="K62" s="4">
+        <v>5</v>
+      </c>
+      <c r="L62" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M62" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P62" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q62" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="R62" s="4">
+        <v>1</v>
+      </c>
+      <c r="S62" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T62" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U62" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V62" s="4">
+        <v>3</v>
+      </c>
+      <c r="W62" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X62" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z62" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA62" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB62" s="4"/>
+      <c r="AC62" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD62" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE62" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF62" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG62" s="4">
+        <v>60</v>
+      </c>
+      <c r="AH62" s="4">
+        <v>30</v>
+      </c>
+      <c r="AI62" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ62" s="4">
+        <v>5.24980189942734E-2</v>
+      </c>
+      <c r="AK62" s="4">
+        <v>6.7667956682833002E-3</v>
+      </c>
+      <c r="AL62" s="4">
+        <v>0.90875402660202564</v>
+      </c>
+      <c r="AM62" s="4">
+        <v>-3.979388929858604</v>
+      </c>
+      <c r="AN62" s="4">
+        <v>8.3188113449148993E-3</v>
+      </c>
+      <c r="AO62" s="4">
+        <v>0.93959467375778205</v>
+      </c>
+      <c r="AP62" s="4">
+        <v>8.3188113449148993E-3</v>
+      </c>
+      <c r="AQ62" s="4">
+        <v>8.3188113449148993E-3</v>
+      </c>
+      <c r="AR62" s="4">
+        <v>0.93959467375778205</v>
+      </c>
+      <c r="AS62" s="4">
+        <v>0.39869083919171788</v>
+      </c>
+      <c r="AT62" s="4">
+        <v>-1.8950109832555251</v>
+      </c>
+      <c r="AU62" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV62" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW62" s="4">
+        <v>8.3188113449148993E-3</v>
+      </c>
+      <c r="AX62" s="4">
+        <v>0.93959467375778205</v>
+      </c>
+      <c r="AY62" s="4">
+        <v>8.3188113449148993E-3</v>
+      </c>
+      <c r="AZ62" s="4">
+        <v>8.3188113449148993E-3</v>
+      </c>
+      <c r="BA62" s="4">
+        <v>0.93959467375778205</v>
+      </c>
+      <c r="BB62" s="4">
+        <v>0.39869083919171788</v>
+      </c>
+      <c r="BC62" s="4">
+        <v>-1.8950109832555251</v>
+      </c>
+      <c r="BD62" s="4"/>
+      <c r="BE62" s="4"/>
+      <c r="BF62" s="4"/>
+      <c r="BG62" s="4"/>
+      <c r="BH62" s="4"/>
+      <c r="BI62" s="4"/>
+      <c r="BJ62" s="4"/>
+      <c r="BK62" s="4"/>
+      <c r="BL62" s="4"/>
+      <c r="BM62" s="4"/>
+      <c r="BN62" s="4"/>
+      <c r="BO62" s="4"/>
+      <c r="BP62" s="4"/>
+      <c r="BQ62" s="4"/>
+      <c r="BR62" s="4"/>
+      <c r="BS62" s="4"/>
+      <c r="BT62" s="4"/>
+      <c r="BU62" s="4"/>
+      <c r="BV62" s="4"/>
+      <c r="BW62" s="4"/>
+      <c r="BX62" s="4"/>
+    </row>
+    <row r="63" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A63" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C63" s="4">
+        <v>1</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F63" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G63" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J63" s="4">
+        <v>5</v>
+      </c>
+      <c r="K63" s="4">
+        <v>5</v>
+      </c>
+      <c r="L63" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M63" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P63" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q63" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="R63" s="4">
+        <v>1</v>
+      </c>
+      <c r="S63" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T63" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U63" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V63" s="4">
+        <v>3</v>
+      </c>
+      <c r="W63" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z63" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA63" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB63" s="4"/>
+      <c r="AC63" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD63" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE63" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF63" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG63" s="4">
+        <v>60</v>
+      </c>
+      <c r="AH63" s="4">
+        <v>30</v>
+      </c>
+      <c r="AI63" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ63" s="4">
+        <v>4.7813806640621702E-2</v>
+      </c>
+      <c r="AK63" s="4">
+        <v>9.1831812317513997E-3</v>
+      </c>
+      <c r="AL63" s="4">
+        <v>0.87617059071125469</v>
+      </c>
+      <c r="AM63" s="4">
+        <v>-1.4858839294878849</v>
+      </c>
+      <c r="AN63" s="4">
+        <v>1.3639119120835101E-2</v>
+      </c>
+      <c r="AO63" s="4">
+        <v>0.90096236036724919</v>
+      </c>
+      <c r="AP63" s="4">
+        <v>1.3639119120835101E-2</v>
+      </c>
+      <c r="AQ63" s="4">
+        <v>1.3639119120835101E-2</v>
+      </c>
+      <c r="AR63" s="4">
+        <v>0.90096236036724919</v>
+      </c>
+      <c r="AS63" s="4">
+        <v>0.26335297152539489</v>
+      </c>
+      <c r="AT63" s="4">
+        <v>-0.91228307774681239</v>
+      </c>
+      <c r="AU63" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV63" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW63" s="4">
+        <v>1.3639119120835101E-2</v>
+      </c>
+      <c r="AX63" s="4">
+        <v>0.90096236036724919</v>
+      </c>
+      <c r="AY63" s="4">
+        <v>1.3639119120835101E-2</v>
+      </c>
+      <c r="AZ63" s="4">
+        <v>1.3639119120835101E-2</v>
+      </c>
+      <c r="BA63" s="4">
+        <v>0.90096236036724919</v>
+      </c>
+      <c r="BB63" s="4">
+        <v>0.26335297152539489</v>
+      </c>
+      <c r="BC63" s="4">
+        <v>-0.91228307774681239</v>
+      </c>
+      <c r="BD63" s="4"/>
+      <c r="BE63" s="4"/>
+      <c r="BF63" s="4"/>
+      <c r="BG63" s="4"/>
+      <c r="BH63" s="4"/>
+      <c r="BI63" s="4"/>
+      <c r="BJ63" s="4"/>
+      <c r="BK63" s="4"/>
+      <c r="BL63" s="4"/>
+      <c r="BM63" s="4"/>
+      <c r="BN63" s="4"/>
+      <c r="BO63" s="4"/>
+      <c r="BP63" s="4"/>
+      <c r="BQ63" s="4"/>
+      <c r="BR63" s="4"/>
+      <c r="BS63" s="4"/>
+      <c r="BT63" s="4"/>
+      <c r="BU63" s="4"/>
+      <c r="BV63" s="4"/>
+      <c r="BW63" s="4"/>
+      <c r="BX63" s="4"/>
+    </row>
+    <row r="64" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C64" s="4">
+        <v>2</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F64" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G64" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J64" s="4">
+        <v>5</v>
+      </c>
+      <c r="K64" s="4">
+        <v>5</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M64" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N64" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O64" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P64" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q64" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="R64" s="4">
+        <v>1</v>
+      </c>
+      <c r="S64" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T64" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U64" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V64" s="4">
+        <v>3</v>
+      </c>
+      <c r="W64" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X64" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z64" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA64" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB64" s="4"/>
+      <c r="AC64" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD64" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE64" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF64" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG64" s="4">
+        <v>60</v>
+      </c>
+      <c r="AH64" s="4">
+        <v>30</v>
+      </c>
+      <c r="AI64" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ64" s="4">
+        <v>4.99795722724602E-2</v>
+      </c>
+      <c r="AK64" s="4">
+        <v>8.2549948709592993E-3</v>
+      </c>
+      <c r="AL64" s="4">
+        <v>0.88868659860287202</v>
+      </c>
+      <c r="AM64" s="4">
+        <v>-1.940912877571997</v>
+      </c>
+      <c r="AN64" s="4">
+        <v>1.8312135645938001E-2</v>
+      </c>
+      <c r="AO64" s="4">
+        <v>0.86703021837839844</v>
+      </c>
+      <c r="AP64" s="4">
+        <v>1.8312135645938001E-2</v>
+      </c>
+      <c r="AQ64" s="4">
+        <v>1.8312135645938001E-2</v>
+      </c>
+      <c r="AR64" s="4">
+        <v>0.86703021837839844</v>
+      </c>
+      <c r="AS64" s="4">
+        <v>0.27078010169161187</v>
+      </c>
+      <c r="AT64" s="4">
+        <v>-0.96621364572489243</v>
+      </c>
+      <c r="AU64" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV64" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW64" s="4">
+        <v>1.8312135645938001E-2</v>
+      </c>
+      <c r="AX64" s="4">
+        <v>0.86703021837839844</v>
+      </c>
+      <c r="AY64" s="4">
+        <v>1.8312135645938001E-2</v>
+      </c>
+      <c r="AZ64" s="4">
+        <v>1.8312135645938001E-2</v>
+      </c>
+      <c r="BA64" s="4">
+        <v>0.86703021837839844</v>
+      </c>
+      <c r="BB64" s="4">
+        <v>0.27078010169161187</v>
+      </c>
+      <c r="BC64" s="4">
+        <v>-0.96621364572489243</v>
+      </c>
+      <c r="BD64" s="4"/>
+      <c r="BE64" s="4"/>
+      <c r="BF64" s="4"/>
+      <c r="BG64" s="4"/>
+      <c r="BH64" s="4"/>
+      <c r="BI64" s="4"/>
+      <c r="BJ64" s="4"/>
+      <c r="BK64" s="4"/>
+      <c r="BL64" s="4"/>
+      <c r="BM64" s="4"/>
+      <c r="BN64" s="4"/>
+      <c r="BO64" s="4"/>
+      <c r="BP64" s="4"/>
+      <c r="BQ64" s="4"/>
+      <c r="BR64" s="4"/>
+      <c r="BS64" s="4"/>
+      <c r="BT64" s="4"/>
+      <c r="BU64" s="4"/>
+      <c r="BV64" s="4"/>
+      <c r="BW64" s="4"/>
+      <c r="BX64" s="4"/>
+    </row>
+    <row r="65" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A65" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C65" s="4">
+        <v>3</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F65" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G65" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J65" s="4">
+        <v>5</v>
+      </c>
+      <c r="K65" s="4">
+        <v>5</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M65" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N65" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O65" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P65" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q65" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="R65" s="4">
+        <v>1</v>
+      </c>
+      <c r="S65" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T65" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U65" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V65" s="4">
+        <v>3</v>
+      </c>
+      <c r="W65" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X65" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z65" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA65" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB65" s="4"/>
+      <c r="AC65" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD65" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE65" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF65" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG65" s="4">
+        <v>60</v>
+      </c>
+      <c r="AH65" s="4">
+        <v>30</v>
+      </c>
+      <c r="AI65" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ65" s="4">
+        <v>6.54721526937459E-2</v>
+      </c>
+      <c r="AK65" s="4">
+        <v>1.25834526252532E-2</v>
+      </c>
+      <c r="AL65" s="4">
+        <v>0.83032007470238678</v>
+      </c>
+      <c r="AM65" s="4">
+        <v>-6.5130716600259E-2</v>
+      </c>
+      <c r="AN65" s="4">
+        <v>1.68929622643656E-2</v>
+      </c>
+      <c r="AO65" s="4">
+        <v>0.87733525206095164</v>
+      </c>
+      <c r="AP65" s="4">
+        <v>1.68929622643656E-2</v>
+      </c>
+      <c r="AQ65" s="4">
+        <v>1.68929622643656E-2</v>
+      </c>
+      <c r="AR65" s="4">
+        <v>0.87733525206095164</v>
+      </c>
+      <c r="AS65" s="4">
+        <v>0.13966442091699999</v>
+      </c>
+      <c r="AT65" s="4">
+        <v>-1.41442761625836E-2</v>
+      </c>
+      <c r="AU65" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV65" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW65" s="4">
+        <v>1.68929622643656E-2</v>
+      </c>
+      <c r="AX65" s="4">
+        <v>0.87733525206095164</v>
+      </c>
+      <c r="AY65" s="4">
+        <v>1.68929622643656E-2</v>
+      </c>
+      <c r="AZ65" s="4">
+        <v>1.68929622643656E-2</v>
+      </c>
+      <c r="BA65" s="4">
+        <v>0.87733525206095164</v>
+      </c>
+      <c r="BB65" s="4">
+        <v>0.13966442091699999</v>
+      </c>
+      <c r="BC65" s="4">
+        <v>-1.41442761625836E-2</v>
+      </c>
+      <c r="BD65" s="4"/>
+      <c r="BE65" s="4"/>
+      <c r="BF65" s="4"/>
+      <c r="BG65" s="4"/>
+      <c r="BH65" s="4"/>
+      <c r="BI65" s="4"/>
+      <c r="BJ65" s="4"/>
+      <c r="BK65" s="4"/>
+      <c r="BL65" s="4"/>
+      <c r="BM65" s="4"/>
+      <c r="BN65" s="4"/>
+      <c r="BO65" s="4"/>
+      <c r="BP65" s="4"/>
+      <c r="BQ65" s="4"/>
+      <c r="BR65" s="4"/>
+      <c r="BS65" s="4"/>
+      <c r="BT65" s="4"/>
+      <c r="BU65" s="4"/>
+      <c r="BV65" s="4"/>
+      <c r="BW65" s="4"/>
+      <c r="BX65" s="4"/>
+    </row>
+    <row r="66" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A66" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C66" s="4">
+        <v>4</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F66" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G66" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J66" s="4">
+        <v>5</v>
+      </c>
+      <c r="K66" s="4">
+        <v>5</v>
+      </c>
+      <c r="L66" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M66" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N66" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O66" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P66" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q66" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="R66" s="4">
+        <v>1</v>
+      </c>
+      <c r="S66" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T66" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U66" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V66" s="4">
+        <v>3</v>
+      </c>
+      <c r="W66" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X66" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z66" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA66" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB66" s="4"/>
+      <c r="AC66" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD66" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE66" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF66" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG66" s="4">
+        <v>60</v>
+      </c>
+      <c r="AH66" s="4">
+        <v>30</v>
+      </c>
+      <c r="AI66" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ66" s="4">
+        <v>4.6903536905258503E-2</v>
+      </c>
+      <c r="AK66" s="4">
+        <v>7.7454084142214996E-3</v>
+      </c>
+      <c r="AL66" s="4">
+        <v>0.89555805069849237</v>
+      </c>
+      <c r="AM66" s="4">
+        <v>-3.821182903610707</v>
+      </c>
+      <c r="AN66" s="4">
+        <v>9.6868306292309005E-3</v>
+      </c>
+      <c r="AO66" s="4">
+        <v>0.92966108496143718</v>
+      </c>
+      <c r="AP66" s="4">
+        <v>9.6868306292309005E-3</v>
+      </c>
+      <c r="AQ66" s="4">
+        <v>9.6868306292309005E-3</v>
+      </c>
+      <c r="AR66" s="4">
+        <v>0.92966108496143718</v>
+      </c>
+      <c r="AS66" s="4">
+        <v>0.39728849169111208</v>
+      </c>
+      <c r="AT66" s="4">
+        <v>-1.884828127223956</v>
+      </c>
+      <c r="AU66" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV66" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW66" s="4">
+        <v>9.6868306292309005E-3</v>
+      </c>
+      <c r="AX66" s="4">
+        <v>0.92966108496143718</v>
+      </c>
+      <c r="AY66" s="4">
+        <v>9.6868306292309005E-3</v>
+      </c>
+      <c r="AZ66" s="4">
+        <v>9.6868306292309005E-3</v>
+      </c>
+      <c r="BA66" s="4">
+        <v>0.92966108496143718</v>
+      </c>
+      <c r="BB66" s="4">
+        <v>0.39728849169111208</v>
+      </c>
+      <c r="BC66" s="4">
+        <v>-1.884828127223956</v>
+      </c>
+      <c r="BD66" s="4"/>
+      <c r="BE66" s="4"/>
+      <c r="BF66" s="4"/>
+      <c r="BG66" s="4"/>
+      <c r="BH66" s="4"/>
+      <c r="BI66" s="4"/>
+      <c r="BJ66" s="4"/>
+      <c r="BK66" s="4"/>
+      <c r="BL66" s="4"/>
+      <c r="BM66" s="4"/>
+      <c r="BN66" s="4"/>
+      <c r="BO66" s="4"/>
+      <c r="BP66" s="4"/>
+      <c r="BQ66" s="4"/>
+      <c r="BR66" s="4"/>
+      <c r="BS66" s="4"/>
+      <c r="BT66" s="4"/>
+      <c r="BU66" s="4"/>
+      <c r="BV66" s="4"/>
+      <c r="BW66" s="4"/>
+      <c r="BX66" s="4"/>
+    </row>
+    <row r="67" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A67" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C67" s="4">
+        <v>5</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F67" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G67" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J67" s="4">
+        <v>5</v>
+      </c>
+      <c r="K67" s="4">
+        <v>5</v>
+      </c>
+      <c r="L67" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M67" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N67" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O67" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P67" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q67" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="R67" s="4">
+        <v>1</v>
+      </c>
+      <c r="S67" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T67" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U67" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V67" s="4">
+        <v>3</v>
+      </c>
+      <c r="W67" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X67" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y67" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z67" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA67" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB67" s="4"/>
+      <c r="AC67" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD67" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE67" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF67" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG67" s="4">
+        <v>60</v>
+      </c>
+      <c r="AH67" s="4">
+        <v>30</v>
+      </c>
+      <c r="AI67" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ67" s="4">
+        <v>4.1046464925833602E-2</v>
+      </c>
+      <c r="AK67" s="4">
+        <v>7.5437417070926003E-3</v>
+      </c>
+      <c r="AL67" s="4">
+        <v>0.89827739910148752</v>
+      </c>
+      <c r="AM67" s="4">
+        <v>-1.6322216513585579</v>
+      </c>
+      <c r="AN67" s="4">
+        <v>2.2185220912376201E-2</v>
+      </c>
+      <c r="AO67" s="4">
+        <v>0.83890661160540292</v>
+      </c>
+      <c r="AP67" s="4">
+        <v>2.2185220912376201E-2</v>
+      </c>
+      <c r="AQ67" s="4">
+        <v>2.2185220912376201E-2</v>
+      </c>
+      <c r="AR67" s="4">
+        <v>0.83890661160540292</v>
+      </c>
+      <c r="AS67" s="4">
+        <v>0.24565052790473149</v>
+      </c>
+      <c r="AT67" s="4">
+        <v>-0.78374044853521374</v>
+      </c>
+      <c r="AU67" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV67" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW67" s="4">
+        <v>2.2185220912376201E-2</v>
+      </c>
+      <c r="AX67" s="4">
+        <v>0.83890661160540292</v>
+      </c>
+      <c r="AY67" s="4">
+        <v>2.2185220912376201E-2</v>
+      </c>
+      <c r="AZ67" s="4">
+        <v>2.2185220912376201E-2</v>
+      </c>
+      <c r="BA67" s="4">
+        <v>0.83890661160540292</v>
+      </c>
+      <c r="BB67" s="4">
+        <v>0.24565052790473149</v>
+      </c>
+      <c r="BC67" s="4">
+        <v>-0.78374044853521374</v>
+      </c>
+      <c r="BD67" s="4"/>
+      <c r="BE67" s="4"/>
+      <c r="BF67" s="4"/>
+      <c r="BG67" s="4"/>
+      <c r="BH67" s="4"/>
+      <c r="BI67" s="4"/>
+      <c r="BJ67" s="4"/>
+      <c r="BK67" s="4"/>
+      <c r="BL67" s="4"/>
+      <c r="BM67" s="4"/>
+      <c r="BN67" s="4"/>
+      <c r="BO67" s="4"/>
+      <c r="BP67" s="4"/>
+      <c r="BQ67" s="4"/>
+      <c r="BR67" s="4"/>
+      <c r="BS67" s="4"/>
+      <c r="BT67" s="4"/>
+      <c r="BU67" s="4"/>
+      <c r="BV67" s="4"/>
+      <c r="BW67" s="4"/>
+      <c r="BX67" s="4"/>
+    </row>
+    <row r="68" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A68" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C68" s="4">
+        <v>6</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F68" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G68" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J68" s="4">
+        <v>5</v>
+      </c>
+      <c r="K68" s="4">
+        <v>5</v>
+      </c>
+      <c r="L68" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M68" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N68" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O68" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P68" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q68" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="R68" s="4">
+        <v>1</v>
+      </c>
+      <c r="S68" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T68" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U68" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V68" s="4">
+        <v>3</v>
+      </c>
+      <c r="W68" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X68" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z68" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA68" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB68" s="4"/>
+      <c r="AC68" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD68" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE68" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF68" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG68" s="4">
+        <v>60</v>
+      </c>
+      <c r="AH68" s="4">
+        <v>30</v>
+      </c>
+      <c r="AI68" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ68" s="4">
+        <v>6.5220637653753702E-2</v>
+      </c>
+      <c r="AK68" s="4">
+        <v>1.30369493559134E-2</v>
+      </c>
+      <c r="AL68" s="4">
+        <v>0.82420495720063691</v>
+      </c>
+      <c r="AM68" s="4">
+        <v>-0.9619399361691624</v>
+      </c>
+      <c r="AN68" s="4">
+        <v>2.7410241160662301E-2</v>
+      </c>
+      <c r="AO68" s="4">
+        <v>0.80096620886831604</v>
+      </c>
+      <c r="AP68" s="4">
+        <v>2.7410241160662301E-2</v>
+      </c>
+      <c r="AQ68" s="4">
+        <v>2.7410241160662301E-2</v>
+      </c>
+      <c r="AR68" s="4">
+        <v>0.80096620886831604</v>
+      </c>
+      <c r="AS68" s="4">
+        <v>0.19794835292275631</v>
+      </c>
+      <c r="AT68" s="4">
+        <v>-0.43736098123175737</v>
+      </c>
+      <c r="AU68" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV68" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW68" s="4">
+        <v>2.7410241160662301E-2</v>
+      </c>
+      <c r="AX68" s="4">
+        <v>0.80096620886831604</v>
+      </c>
+      <c r="AY68" s="4">
+        <v>2.7410241160662301E-2</v>
+      </c>
+      <c r="AZ68" s="4">
+        <v>2.7410241160662301E-2</v>
+      </c>
+      <c r="BA68" s="4">
+        <v>0.80096620886831604</v>
+      </c>
+      <c r="BB68" s="4">
+        <v>0.19794835292275631</v>
+      </c>
+      <c r="BC68" s="4">
+        <v>-0.43736098123175737</v>
+      </c>
+      <c r="BD68" s="4"/>
+      <c r="BE68" s="4"/>
+      <c r="BF68" s="4"/>
+      <c r="BG68" s="4"/>
+      <c r="BH68" s="4"/>
+      <c r="BI68" s="4"/>
+      <c r="BJ68" s="4"/>
+      <c r="BK68" s="4"/>
+      <c r="BL68" s="4"/>
+      <c r="BM68" s="4"/>
+      <c r="BN68" s="4"/>
+      <c r="BO68" s="4"/>
+      <c r="BP68" s="4"/>
+      <c r="BQ68" s="4"/>
+      <c r="BR68" s="4"/>
+      <c r="BS68" s="4"/>
+      <c r="BT68" s="4"/>
+      <c r="BU68" s="4"/>
+      <c r="BV68" s="4"/>
+      <c r="BW68" s="4"/>
+      <c r="BX68" s="4"/>
+    </row>
+    <row r="69" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A69" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C69" s="4">
+        <v>7</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F69" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G69" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J69" s="4">
+        <v>5</v>
+      </c>
+      <c r="K69" s="4">
+        <v>5</v>
+      </c>
+      <c r="L69" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M69" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N69" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O69" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P69" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q69" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="R69" s="4">
+        <v>1</v>
+      </c>
+      <c r="S69" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T69" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U69" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V69" s="4">
+        <v>3</v>
+      </c>
+      <c r="W69" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X69" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z69" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA69" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB69" s="4"/>
+      <c r="AC69" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD69" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE69" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF69" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG69" s="4">
+        <v>60</v>
+      </c>
+      <c r="AH69" s="4">
+        <v>30</v>
+      </c>
+      <c r="AI69" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ69" s="4">
+        <v>5.6598803148057299E-2</v>
+      </c>
+      <c r="AK69" s="4">
+        <v>7.4804008067730996E-3</v>
+      </c>
+      <c r="AL69" s="4">
+        <v>0.89913151120844048</v>
+      </c>
+      <c r="AM69" s="4">
+        <v>-1.256008985190856</v>
+      </c>
+      <c r="AN69" s="4">
+        <v>2.06104551793777E-2</v>
+      </c>
+      <c r="AO69" s="4">
+        <v>0.85034144693376768</v>
+      </c>
+      <c r="AP69" s="4">
+        <v>2.06104551793777E-2</v>
+      </c>
+      <c r="AQ69" s="4">
+        <v>2.06104551793777E-2</v>
+      </c>
+      <c r="AR69" s="4">
+        <v>0.85034144693376768</v>
+      </c>
+      <c r="AS69" s="4">
+        <v>0.22361408734599789</v>
+      </c>
+      <c r="AT69" s="4">
+        <v>-0.62372739787488984</v>
+      </c>
+      <c r="AU69" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV69" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW69" s="4">
+        <v>2.06104551793777E-2</v>
+      </c>
+      <c r="AX69" s="4">
+        <v>0.85034144693376768</v>
+      </c>
+      <c r="AY69" s="4">
+        <v>2.06104551793777E-2</v>
+      </c>
+      <c r="AZ69" s="4">
+        <v>2.06104551793777E-2</v>
+      </c>
+      <c r="BA69" s="4">
+        <v>0.85034144693376768</v>
+      </c>
+      <c r="BB69" s="4">
+        <v>0.22361408734599789</v>
+      </c>
+      <c r="BC69" s="4">
+        <v>-0.62372739787488984</v>
+      </c>
+      <c r="BD69" s="4"/>
+      <c r="BE69" s="4"/>
+      <c r="BF69" s="4"/>
+      <c r="BG69" s="4"/>
+      <c r="BH69" s="4"/>
+      <c r="BI69" s="4"/>
+      <c r="BJ69" s="4"/>
+      <c r="BK69" s="4"/>
+      <c r="BL69" s="4"/>
+      <c r="BM69" s="4"/>
+      <c r="BN69" s="4"/>
+      <c r="BO69" s="4"/>
+      <c r="BP69" s="4"/>
+      <c r="BQ69" s="4"/>
+      <c r="BR69" s="4"/>
+      <c r="BS69" s="4"/>
+      <c r="BT69" s="4"/>
+      <c r="BU69" s="4"/>
+      <c r="BV69" s="4"/>
+      <c r="BW69" s="4"/>
+      <c r="BX69" s="4"/>
+    </row>
+    <row r="70" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A70" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C70" s="4">
+        <v>8</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F70" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G70" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J70" s="4">
+        <v>5</v>
+      </c>
+      <c r="K70" s="4">
+        <v>5</v>
+      </c>
+      <c r="L70" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M70" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N70" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O70" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P70" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q70" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="R70" s="4">
+        <v>1</v>
+      </c>
+      <c r="S70" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T70" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U70" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V70" s="4">
+        <v>3</v>
+      </c>
+      <c r="W70" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X70" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z70" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA70" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB70" s="4"/>
+      <c r="AC70" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD70" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE70" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF70" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG70" s="4">
+        <v>60</v>
+      </c>
+      <c r="AH70" s="4">
+        <v>30</v>
+      </c>
+      <c r="AI70" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ70" s="4">
+        <v>4.7496318898352201E-2</v>
+      </c>
+      <c r="AK70" s="4">
+        <v>7.5963683606788002E-3</v>
+      </c>
+      <c r="AL70" s="4">
+        <v>0.89756776185683773</v>
+      </c>
+      <c r="AM70" s="4">
+        <v>-3.322739076438268</v>
+      </c>
+      <c r="AN70" s="4">
+        <v>9.9895685131398994E-3</v>
+      </c>
+      <c r="AO70" s="4">
+        <v>0.92746281649672635</v>
+      </c>
+      <c r="AP70" s="4">
+        <v>9.9895685131398994E-3</v>
+      </c>
+      <c r="AQ70" s="4">
+        <v>9.9895685131398994E-3</v>
+      </c>
+      <c r="AR70" s="4">
+        <v>0.92746281649672635</v>
+      </c>
+      <c r="AS70" s="4">
+        <v>0.36430719603296868</v>
+      </c>
+      <c r="AT70" s="4">
+        <v>-1.645341277298094</v>
+      </c>
+      <c r="AU70" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV70" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW70" s="4">
+        <v>9.9895685131398994E-3</v>
+      </c>
+      <c r="AX70" s="4">
+        <v>0.92746281649672635</v>
+      </c>
+      <c r="AY70" s="4">
+        <v>9.9895685131398994E-3</v>
+      </c>
+      <c r="AZ70" s="4">
+        <v>9.9895685131398994E-3</v>
+      </c>
+      <c r="BA70" s="4">
+        <v>0.92746281649672635</v>
+      </c>
+      <c r="BB70" s="4">
+        <v>0.36430719603296868</v>
+      </c>
+      <c r="BC70" s="4">
+        <v>-1.645341277298094</v>
+      </c>
+      <c r="BD70" s="4"/>
+      <c r="BE70" s="4"/>
+      <c r="BF70" s="4"/>
+      <c r="BG70" s="4"/>
+      <c r="BH70" s="4"/>
+      <c r="BI70" s="4"/>
+      <c r="BJ70" s="4"/>
+      <c r="BK70" s="4"/>
+      <c r="BL70" s="4"/>
+      <c r="BM70" s="4"/>
+      <c r="BN70" s="4"/>
+      <c r="BO70" s="4"/>
+      <c r="BP70" s="4"/>
+      <c r="BQ70" s="4"/>
+      <c r="BR70" s="4"/>
+      <c r="BS70" s="4"/>
+      <c r="BT70" s="4"/>
+      <c r="BU70" s="4"/>
+      <c r="BV70" s="4"/>
+      <c r="BW70" s="4"/>
+      <c r="BX70" s="4"/>
+    </row>
+    <row r="71" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A71" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C71" s="4">
+        <v>9</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F71" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G71" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I71" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J71" s="4">
+        <v>5</v>
+      </c>
+      <c r="K71" s="4">
+        <v>5</v>
+      </c>
+      <c r="L71" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M71" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N71" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O71" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P71" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q71" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="R71" s="4">
+        <v>1</v>
+      </c>
+      <c r="S71" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T71" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U71" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V71" s="4">
+        <v>3</v>
+      </c>
+      <c r="W71" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X71" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z71" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA71" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB71" s="4"/>
+      <c r="AC71" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD71" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE71" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF71" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG71" s="4">
+        <v>60</v>
+      </c>
+      <c r="AH71" s="4">
+        <v>30</v>
+      </c>
+      <c r="AI71" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ71" s="4">
+        <v>6.5685582300247902E-2</v>
+      </c>
+      <c r="AK71" s="4">
+        <v>7.6725183679851004E-3</v>
+      </c>
+      <c r="AL71" s="4">
+        <v>0.89654092701778787</v>
+      </c>
+      <c r="AM71" s="4">
+        <v>-1.5200695029441931</v>
+      </c>
+      <c r="AN71" s="4">
+        <v>2.2135973223606501E-2</v>
+      </c>
+      <c r="AO71" s="4">
+        <v>0.83926421350109015</v>
+      </c>
+      <c r="AP71" s="4">
+        <v>2.2135973223606501E-2</v>
+      </c>
+      <c r="AQ71" s="4">
+        <v>2.2135973223606501E-2</v>
+      </c>
+      <c r="AR71" s="4">
+        <v>0.83926421350109015</v>
+      </c>
+      <c r="AS71" s="4">
+        <v>0.2390732672655411</v>
+      </c>
+      <c r="AT71" s="4">
+        <v>-0.73598103216940558</v>
+      </c>
+      <c r="AU71" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV71" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW71" s="4">
+        <v>2.2135973223606501E-2</v>
+      </c>
+      <c r="AX71" s="4">
+        <v>0.83926421350109015</v>
+      </c>
+      <c r="AY71" s="4">
+        <v>2.2135973223606501E-2</v>
+      </c>
+      <c r="AZ71" s="4">
+        <v>2.2135973223606501E-2</v>
+      </c>
+      <c r="BA71" s="4">
+        <v>0.83926421350109015</v>
+      </c>
+      <c r="BB71" s="4">
+        <v>0.2390732672655411</v>
+      </c>
+      <c r="BC71" s="4">
+        <v>-0.73598103216940558</v>
+      </c>
+      <c r="BD71" s="4"/>
+      <c r="BE71" s="4"/>
+      <c r="BF71" s="4"/>
+      <c r="BG71" s="4"/>
+      <c r="BH71" s="4"/>
+      <c r="BI71" s="4"/>
+      <c r="BJ71" s="4"/>
+      <c r="BK71" s="4"/>
+      <c r="BL71" s="4"/>
+      <c r="BM71" s="4"/>
+      <c r="BN71" s="4"/>
+      <c r="BO71" s="4"/>
+      <c r="BP71" s="4"/>
+      <c r="BQ71" s="4"/>
+      <c r="BR71" s="4"/>
+      <c r="BS71" s="4"/>
+      <c r="BT71" s="4"/>
+      <c r="BU71" s="4"/>
+      <c r="BV71" s="4"/>
+      <c r="BW71" s="4"/>
+      <c r="BX71" s="4"/>
+    </row>
+    <row r="72" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A72" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C72" s="4">
+        <v>0</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F72" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G72" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J72" s="4">
+        <v>5</v>
+      </c>
+      <c r="K72" s="4">
+        <v>5</v>
+      </c>
+      <c r="L72" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M72" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N72" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O72" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P72" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q72" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R72" s="4">
+        <v>1</v>
+      </c>
+      <c r="S72" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T72" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U72" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V72" s="4">
+        <v>5</v>
+      </c>
+      <c r="W72" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X72" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z72" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA72" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB72" s="4"/>
+      <c r="AC72" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD72" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE72" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF72" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG72" s="4">
+        <v>80</v>
+      </c>
+      <c r="AH72" s="4">
+        <v>50</v>
+      </c>
+      <c r="AI72" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ72" s="4">
+        <v>5.1501777242581002E-2</v>
+      </c>
+      <c r="AK72" s="4">
+        <v>1.24343523440227E-2</v>
+      </c>
+      <c r="AL72" s="4">
+        <v>0.83233059799313081</v>
+      </c>
+      <c r="AM72" s="4">
+        <v>8.8039814292093996E-3</v>
+      </c>
+      <c r="AN72" s="4">
+        <v>2.2278997447396899E-2</v>
+      </c>
+      <c r="AO72" s="4">
+        <v>0.83822567271198056</v>
+      </c>
+      <c r="AP72" s="4">
+        <v>2.2278997447396899E-2</v>
+      </c>
+      <c r="AQ72" s="4">
+        <v>2.2278997447396899E-2</v>
+      </c>
+      <c r="AR72" s="4">
+        <v>0.83822567271198056</v>
+      </c>
+      <c r="AS72" s="4">
+        <v>0.13688394625576861</v>
+      </c>
+      <c r="AT72" s="4">
+        <v>6.0455649164030999E-3</v>
+      </c>
+      <c r="AU72" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV72" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW72" s="4">
+        <v>2.2278997447396899E-2</v>
+      </c>
+      <c r="AX72" s="4">
+        <v>0.83822567271198056</v>
+      </c>
+      <c r="AY72" s="4">
+        <v>2.2278997447396899E-2</v>
+      </c>
+      <c r="AZ72" s="4">
+        <v>2.2278997447396899E-2</v>
+      </c>
+      <c r="BA72" s="4">
+        <v>0.83822567271198056</v>
+      </c>
+      <c r="BB72" s="4">
+        <v>0.13688394625576861</v>
+      </c>
+      <c r="BC72" s="4">
+        <v>6.0455649164030999E-3</v>
+      </c>
+      <c r="BD72" s="4"/>
+      <c r="BE72" s="4"/>
+      <c r="BF72" s="4"/>
+      <c r="BG72" s="4"/>
+      <c r="BH72" s="4"/>
+      <c r="BI72" s="4"/>
+      <c r="BJ72" s="4"/>
+      <c r="BK72" s="4"/>
+      <c r="BL72" s="4"/>
+      <c r="BM72" s="4"/>
+      <c r="BN72" s="4"/>
+      <c r="BO72" s="4"/>
+      <c r="BP72" s="4"/>
+      <c r="BQ72" s="4"/>
+      <c r="BR72" s="4"/>
+      <c r="BS72" s="4"/>
+      <c r="BT72" s="4"/>
+      <c r="BU72" s="4"/>
+      <c r="BV72" s="4"/>
+      <c r="BW72" s="4"/>
+      <c r="BX72" s="4"/>
+    </row>
+    <row r="73" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A73" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C73" s="4">
+        <v>1</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F73" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G73" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J73" s="4">
+        <v>5</v>
+      </c>
+      <c r="K73" s="4">
+        <v>5</v>
+      </c>
+      <c r="L73" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M73" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N73" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O73" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P73" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q73" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R73" s="4">
+        <v>1</v>
+      </c>
+      <c r="S73" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T73" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U73" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V73" s="4">
+        <v>5</v>
+      </c>
+      <c r="W73" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X73" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z73" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA73" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB73" s="4"/>
+      <c r="AC73" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD73" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE73" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF73" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG73" s="4">
+        <v>80</v>
+      </c>
+      <c r="AH73" s="4">
+        <v>50</v>
+      </c>
+      <c r="AI73" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ73" s="4">
+        <v>5.4679739548186203E-2</v>
+      </c>
+      <c r="AK73" s="4">
+        <v>9.9393408611481993E-3</v>
+      </c>
+      <c r="AL73" s="4">
+        <v>0.86597425483666102</v>
+      </c>
+      <c r="AM73" s="4">
+        <v>-0.69266200543001211</v>
+      </c>
+      <c r="AN73" s="4">
+        <v>1.73080101567431E-2</v>
+      </c>
+      <c r="AO73" s="4">
+        <v>0.87432146772257613</v>
+      </c>
+      <c r="AP73" s="4">
+        <v>1.73080101567431E-2</v>
+      </c>
+      <c r="AQ73" s="4">
+        <v>1.73080101567431E-2</v>
+      </c>
+      <c r="AR73" s="4">
+        <v>0.87432146772257613</v>
+      </c>
+      <c r="AS73" s="4">
+        <v>0.20787441514176441</v>
+      </c>
+      <c r="AT73" s="4">
+        <v>-0.50943702692862858</v>
+      </c>
+      <c r="AU73" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV73" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW73" s="4">
+        <v>1.73080101567431E-2</v>
+      </c>
+      <c r="AX73" s="4">
+        <v>0.87432146772257613</v>
+      </c>
+      <c r="AY73" s="4">
+        <v>1.73080101567431E-2</v>
+      </c>
+      <c r="AZ73" s="4">
+        <v>1.73080101567431E-2</v>
+      </c>
+      <c r="BA73" s="4">
+        <v>0.87432146772257613</v>
+      </c>
+      <c r="BB73" s="4">
+        <v>0.20787441514176441</v>
+      </c>
+      <c r="BC73" s="4">
+        <v>-0.50943702692862858</v>
+      </c>
+      <c r="BD73" s="4"/>
+      <c r="BE73" s="4"/>
+      <c r="BF73" s="4"/>
+      <c r="BG73" s="4"/>
+      <c r="BH73" s="4"/>
+      <c r="BI73" s="4"/>
+      <c r="BJ73" s="4"/>
+      <c r="BK73" s="4"/>
+      <c r="BL73" s="4"/>
+      <c r="BM73" s="4"/>
+      <c r="BN73" s="4"/>
+      <c r="BO73" s="4"/>
+      <c r="BP73" s="4"/>
+      <c r="BQ73" s="4"/>
+      <c r="BR73" s="4"/>
+      <c r="BS73" s="4"/>
+      <c r="BT73" s="4"/>
+      <c r="BU73" s="4"/>
+      <c r="BV73" s="4"/>
+      <c r="BW73" s="4"/>
+      <c r="BX73" s="4"/>
+    </row>
+    <row r="74" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A74" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C74" s="4">
+        <v>2</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F74" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G74" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J74" s="4">
+        <v>5</v>
+      </c>
+      <c r="K74" s="4">
+        <v>5</v>
+      </c>
+      <c r="L74" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M74" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N74" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O74" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P74" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q74" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R74" s="4">
+        <v>1</v>
+      </c>
+      <c r="S74" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T74" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U74" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V74" s="4">
+        <v>5</v>
+      </c>
+      <c r="W74" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X74" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z74" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA74" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB74" s="4"/>
+      <c r="AC74" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD74" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE74" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF74" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG74" s="4">
+        <v>80</v>
+      </c>
+      <c r="AH74" s="4">
+        <v>50</v>
+      </c>
+      <c r="AI74" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ74" s="4">
+        <v>5.7020440968613098E-2</v>
+      </c>
+      <c r="AK74" s="4">
+        <v>1.31941874239743E-2</v>
+      </c>
+      <c r="AL74" s="4">
+        <v>0.82208470098502717</v>
+      </c>
+      <c r="AM74" s="4">
+        <v>-0.32071081911185018</v>
+      </c>
+      <c r="AN74" s="4">
+        <v>2.51065775289862E-2</v>
+      </c>
+      <c r="AO74" s="4">
+        <v>0.81769378537584059</v>
+      </c>
+      <c r="AP74" s="4">
+        <v>2.51065775289862E-2</v>
+      </c>
+      <c r="AQ74" s="4">
+        <v>2.51065775289862E-2</v>
+      </c>
+      <c r="AR74" s="4">
+        <v>0.81769378537584059</v>
+      </c>
+      <c r="AS74" s="4">
+        <v>0.1645785268841948</v>
+      </c>
+      <c r="AT74" s="4">
+        <v>-0.195052898390388</v>
+      </c>
+      <c r="AU74" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV74" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW74" s="4">
+        <v>2.51065775289862E-2</v>
+      </c>
+      <c r="AX74" s="4">
+        <v>0.81769378537584059</v>
+      </c>
+      <c r="AY74" s="4">
+        <v>2.51065775289862E-2</v>
+      </c>
+      <c r="AZ74" s="4">
+        <v>2.51065775289862E-2</v>
+      </c>
+      <c r="BA74" s="4">
+        <v>0.81769378537584059</v>
+      </c>
+      <c r="BB74" s="4">
+        <v>0.1645785268841948</v>
+      </c>
+      <c r="BC74" s="4">
+        <v>-0.195052898390388</v>
+      </c>
+      <c r="BD74" s="4"/>
+      <c r="BE74" s="4"/>
+      <c r="BF74" s="4"/>
+      <c r="BG74" s="4"/>
+      <c r="BH74" s="4"/>
+      <c r="BI74" s="4"/>
+      <c r="BJ74" s="4"/>
+      <c r="BK74" s="4"/>
+      <c r="BL74" s="4"/>
+      <c r="BM74" s="4"/>
+      <c r="BN74" s="4"/>
+      <c r="BO74" s="4"/>
+      <c r="BP74" s="4"/>
+      <c r="BQ74" s="4"/>
+      <c r="BR74" s="4"/>
+      <c r="BS74" s="4"/>
+      <c r="BT74" s="4"/>
+      <c r="BU74" s="4"/>
+      <c r="BV74" s="4"/>
+      <c r="BW74" s="4"/>
+      <c r="BX74" s="4"/>
+    </row>
+    <row r="75" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A75" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C75" s="4">
+        <v>3</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F75" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G75" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J75" s="4">
+        <v>5</v>
+      </c>
+      <c r="K75" s="4">
+        <v>5</v>
+      </c>
+      <c r="L75" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M75" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N75" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O75" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P75" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q75" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R75" s="4">
+        <v>1</v>
+      </c>
+      <c r="S75" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T75" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U75" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V75" s="4">
+        <v>5</v>
+      </c>
+      <c r="W75" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X75" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z75" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA75" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB75" s="4"/>
+      <c r="AC75" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD75" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE75" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF75" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG75" s="4">
+        <v>80</v>
+      </c>
+      <c r="AH75" s="4">
+        <v>50</v>
+      </c>
+      <c r="AI75" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ75" s="4">
+        <v>5.1142051352913498E-2</v>
+      </c>
+      <c r="AK75" s="4">
+        <v>8.4451080866467E-3</v>
+      </c>
+      <c r="AL75" s="4">
+        <v>0.88612304174796019</v>
+      </c>
+      <c r="AM75" s="4">
+        <v>-0.7041419475331141</v>
+      </c>
+      <c r="AN75" s="4">
+        <v>1.49686682687214E-2</v>
+      </c>
+      <c r="AO75" s="4">
+        <v>0.89130811450167535</v>
+      </c>
+      <c r="AP75" s="4">
+        <v>1.49686682687214E-2</v>
+      </c>
+      <c r="AQ75" s="4">
+        <v>1.49686682687214E-2</v>
+      </c>
+      <c r="AR75" s="4">
+        <v>0.89130811450167535</v>
+      </c>
+      <c r="AS75" s="4">
+        <v>0.19243431723825349</v>
+      </c>
+      <c r="AT75" s="4">
+        <v>-0.39732195274276272</v>
+      </c>
+      <c r="AU75" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV75" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW75" s="4">
+        <v>1.49686682687214E-2</v>
+      </c>
+      <c r="AX75" s="4">
+        <v>0.89130811450167535</v>
+      </c>
+      <c r="AY75" s="4">
+        <v>1.49686682687214E-2</v>
+      </c>
+      <c r="AZ75" s="4">
+        <v>1.49686682687214E-2</v>
+      </c>
+      <c r="BA75" s="4">
+        <v>0.89130811450167535</v>
+      </c>
+      <c r="BB75" s="4">
+        <v>0.19243431723825349</v>
+      </c>
+      <c r="BC75" s="4">
+        <v>-0.39732195274276272</v>
+      </c>
+      <c r="BD75" s="4"/>
+      <c r="BE75" s="4"/>
+      <c r="BF75" s="4"/>
+      <c r="BG75" s="4"/>
+      <c r="BH75" s="4"/>
+      <c r="BI75" s="4"/>
+      <c r="BJ75" s="4"/>
+      <c r="BK75" s="4"/>
+      <c r="BL75" s="4"/>
+      <c r="BM75" s="4"/>
+      <c r="BN75" s="4"/>
+      <c r="BO75" s="4"/>
+      <c r="BP75" s="4"/>
+      <c r="BQ75" s="4"/>
+      <c r="BR75" s="4"/>
+      <c r="BS75" s="4"/>
+      <c r="BT75" s="4"/>
+      <c r="BU75" s="4"/>
+      <c r="BV75" s="4"/>
+      <c r="BW75" s="4"/>
+      <c r="BX75" s="4"/>
+    </row>
+    <row r="76" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A76" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C76" s="4">
+        <v>4</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F76" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G76" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J76" s="4">
+        <v>5</v>
+      </c>
+      <c r="K76" s="4">
+        <v>5</v>
+      </c>
+      <c r="L76" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M76" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N76" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O76" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P76" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q76" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R76" s="4">
+        <v>1</v>
+      </c>
+      <c r="S76" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T76" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U76" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V76" s="4">
+        <v>5</v>
+      </c>
+      <c r="W76" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X76" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z76" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA76" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB76" s="4"/>
+      <c r="AC76" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD76" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE76" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF76" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG76" s="4">
+        <v>80</v>
+      </c>
+      <c r="AH76" s="4">
+        <v>50</v>
+      </c>
+      <c r="AI76" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ76" s="4">
+        <v>6.6508363572216095E-2</v>
+      </c>
+      <c r="AK76" s="4">
+        <v>1.46360368095675E-2</v>
+      </c>
+      <c r="AL76" s="4">
+        <v>0.80264227104756469</v>
+      </c>
+      <c r="AM76" s="4">
+        <v>-8.3113007182631007E-3</v>
+      </c>
+      <c r="AN76" s="4">
+        <v>2.0861434471526399E-2</v>
+      </c>
+      <c r="AO76" s="4">
+        <v>0.84851901276695063</v>
+      </c>
+      <c r="AP76" s="4">
+        <v>2.0861434471526399E-2</v>
+      </c>
+      <c r="AQ76" s="4">
+        <v>2.0861434471526399E-2</v>
+      </c>
+      <c r="AR76" s="4">
+        <v>0.84851901276695063</v>
+      </c>
+      <c r="AS76" s="4">
+        <v>0.14466359633640269</v>
+      </c>
+      <c r="AT76" s="4">
+        <v>-5.04447534339773E-2</v>
+      </c>
+      <c r="AU76" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV76" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW76" s="4">
+        <v>2.0861434471526399E-2</v>
+      </c>
+      <c r="AX76" s="4">
+        <v>0.84851901276695063</v>
+      </c>
+      <c r="AY76" s="4">
+        <v>2.0861434471526399E-2</v>
+      </c>
+      <c r="AZ76" s="4">
+        <v>2.0861434471526399E-2</v>
+      </c>
+      <c r="BA76" s="4">
+        <v>0.84851901276695063</v>
+      </c>
+      <c r="BB76" s="4">
+        <v>0.14466359633640269</v>
+      </c>
+      <c r="BC76" s="4">
+        <v>-5.04447534339773E-2</v>
+      </c>
+      <c r="BD76" s="4"/>
+      <c r="BE76" s="4"/>
+      <c r="BF76" s="4"/>
+      <c r="BG76" s="4"/>
+      <c r="BH76" s="4"/>
+      <c r="BI76" s="4"/>
+      <c r="BJ76" s="4"/>
+      <c r="BK76" s="4"/>
+      <c r="BL76" s="4"/>
+      <c r="BM76" s="4"/>
+      <c r="BN76" s="4"/>
+      <c r="BO76" s="4"/>
+      <c r="BP76" s="4"/>
+      <c r="BQ76" s="4"/>
+      <c r="BR76" s="4"/>
+      <c r="BS76" s="4"/>
+      <c r="BT76" s="4"/>
+      <c r="BU76" s="4"/>
+      <c r="BV76" s="4"/>
+      <c r="BW76" s="4"/>
+      <c r="BX76" s="4"/>
+    </row>
+    <row r="77" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A77" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C77" s="4">
+        <v>5</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F77" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G77" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J77" s="4">
+        <v>5</v>
+      </c>
+      <c r="K77" s="4">
+        <v>5</v>
+      </c>
+      <c r="L77" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M77" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N77" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O77" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P77" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q77" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R77" s="4">
+        <v>1</v>
+      </c>
+      <c r="S77" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T77" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U77" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V77" s="4">
+        <v>5</v>
+      </c>
+      <c r="W77" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X77" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z77" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA77" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB77" s="4"/>
+      <c r="AC77" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD77" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE77" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF77" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG77" s="4">
+        <v>80</v>
+      </c>
+      <c r="AH77" s="4">
+        <v>50</v>
+      </c>
+      <c r="AI77" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ77" s="4">
+        <v>4.9789650844667001E-2</v>
+      </c>
+      <c r="AK77" s="4">
+        <v>1.04525922434221E-2</v>
+      </c>
+      <c r="AL77" s="4">
+        <v>0.85905338353077054</v>
+      </c>
+      <c r="AM77" s="4">
+        <v>-0.53247617539709591</v>
+      </c>
+      <c r="AN77" s="4">
+        <v>2.1401248777741501E-2</v>
+      </c>
+      <c r="AO77" s="4">
+        <v>0.84459926294631382</v>
+      </c>
+      <c r="AP77" s="4">
+        <v>2.1401248777741501E-2</v>
+      </c>
+      <c r="AQ77" s="4">
+        <v>2.1401248777741501E-2</v>
+      </c>
+      <c r="AR77" s="4">
+        <v>0.84459926294631382</v>
+      </c>
+      <c r="AS77" s="4">
+        <v>0.16702134953353531</v>
+      </c>
+      <c r="AT77" s="4">
+        <v>-0.21279094929299619</v>
+      </c>
+      <c r="AU77" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV77" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW77" s="4">
+        <v>2.1401248777741501E-2</v>
+      </c>
+      <c r="AX77" s="4">
+        <v>0.84459926294631382</v>
+      </c>
+      <c r="AY77" s="4">
+        <v>2.1401248777741501E-2</v>
+      </c>
+      <c r="AZ77" s="4">
+        <v>2.1401248777741501E-2</v>
+      </c>
+      <c r="BA77" s="4">
+        <v>0.84459926294631382</v>
+      </c>
+      <c r="BB77" s="4">
+        <v>0.16702134953353531</v>
+      </c>
+      <c r="BC77" s="4">
+        <v>-0.21279094929299619</v>
+      </c>
+      <c r="BD77" s="4"/>
+      <c r="BE77" s="4"/>
+      <c r="BF77" s="4"/>
+      <c r="BG77" s="4"/>
+      <c r="BH77" s="4"/>
+      <c r="BI77" s="4"/>
+      <c r="BJ77" s="4"/>
+      <c r="BK77" s="4"/>
+      <c r="BL77" s="4"/>
+      <c r="BM77" s="4"/>
+      <c r="BN77" s="4"/>
+      <c r="BO77" s="4"/>
+      <c r="BP77" s="4"/>
+      <c r="BQ77" s="4"/>
+      <c r="BR77" s="4"/>
+      <c r="BS77" s="4"/>
+      <c r="BT77" s="4"/>
+      <c r="BU77" s="4"/>
+      <c r="BV77" s="4"/>
+      <c r="BW77" s="4"/>
+      <c r="BX77" s="4"/>
+    </row>
+    <row r="78" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A78" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C78" s="4">
+        <v>6</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F78" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G78" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J78" s="4">
+        <v>5</v>
+      </c>
+      <c r="K78" s="4">
+        <v>5</v>
+      </c>
+      <c r="L78" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M78" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N78" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O78" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P78" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q78" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R78" s="4">
+        <v>1</v>
+      </c>
+      <c r="S78" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T78" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U78" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V78" s="4">
+        <v>5</v>
+      </c>
+      <c r="W78" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X78" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z78" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA78" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB78" s="4"/>
+      <c r="AC78" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD78" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE78" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF78" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG78" s="4">
+        <v>80</v>
+      </c>
+      <c r="AH78" s="4">
+        <v>50</v>
+      </c>
+      <c r="AI78" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ78" s="4">
+        <v>4.8132765663136803E-2</v>
+      </c>
+      <c r="AK78" s="4">
+        <v>1.0911368194382501E-2</v>
+      </c>
+      <c r="AL78" s="4">
+        <v>0.85286707907160508</v>
+      </c>
+      <c r="AM78" s="4">
+        <v>-0.4776711557474051</v>
+      </c>
+      <c r="AN78" s="4">
+        <v>2.5679205936134101E-2</v>
+      </c>
+      <c r="AO78" s="4">
+        <v>0.81353576275516026</v>
+      </c>
+      <c r="AP78" s="4">
+        <v>2.5679205936134101E-2</v>
+      </c>
+      <c r="AQ78" s="4">
+        <v>2.5679205936134101E-2</v>
+      </c>
+      <c r="AR78" s="4">
+        <v>0.81353576275516026</v>
+      </c>
+      <c r="AS78" s="4">
+        <v>0.1657426803656871</v>
+      </c>
+      <c r="AT78" s="4">
+        <v>-0.20350615786820289</v>
+      </c>
+      <c r="AU78" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV78" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW78" s="4">
+        <v>2.5679205936134101E-2</v>
+      </c>
+      <c r="AX78" s="4">
+        <v>0.81353576275516026</v>
+      </c>
+      <c r="AY78" s="4">
+        <v>2.5679205936134101E-2</v>
+      </c>
+      <c r="AZ78" s="4">
+        <v>2.5679205936134101E-2</v>
+      </c>
+      <c r="BA78" s="4">
+        <v>0.81353576275516026</v>
+      </c>
+      <c r="BB78" s="4">
+        <v>0.1657426803656871</v>
+      </c>
+      <c r="BC78" s="4">
+        <v>-0.20350615786820289</v>
+      </c>
+      <c r="BD78" s="4"/>
+      <c r="BE78" s="4"/>
+      <c r="BF78" s="4"/>
+      <c r="BG78" s="4"/>
+      <c r="BH78" s="4"/>
+      <c r="BI78" s="4"/>
+      <c r="BJ78" s="4"/>
+      <c r="BK78" s="4"/>
+      <c r="BL78" s="4"/>
+      <c r="BM78" s="4"/>
+      <c r="BN78" s="4"/>
+      <c r="BO78" s="4"/>
+      <c r="BP78" s="4"/>
+      <c r="BQ78" s="4"/>
+      <c r="BR78" s="4"/>
+      <c r="BS78" s="4"/>
+      <c r="BT78" s="4"/>
+      <c r="BU78" s="4"/>
+      <c r="BV78" s="4"/>
+      <c r="BW78" s="4"/>
+      <c r="BX78" s="4"/>
+    </row>
+    <row r="79" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C79" s="4">
+        <v>7</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F79" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G79" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J79" s="4">
+        <v>5</v>
+      </c>
+      <c r="K79" s="4">
+        <v>5</v>
+      </c>
+      <c r="L79" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M79" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N79" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O79" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P79" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q79" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R79" s="4">
+        <v>1</v>
+      </c>
+      <c r="S79" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T79" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U79" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V79" s="4">
+        <v>5</v>
+      </c>
+      <c r="W79" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X79" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z79" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA79" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB79" s="4"/>
+      <c r="AC79" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD79" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE79" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF79" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG79" s="4">
+        <v>80</v>
+      </c>
+      <c r="AH79" s="4">
+        <v>50</v>
+      </c>
+      <c r="AI79" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ79" s="4">
+        <v>4.6160804613806998E-2</v>
+      </c>
+      <c r="AK79" s="4">
+        <v>7.8909617796502993E-3</v>
+      </c>
+      <c r="AL79" s="4">
+        <v>0.89359535533114898</v>
+      </c>
+      <c r="AM79" s="4">
+        <v>2.3534514511138999E-2</v>
+      </c>
+      <c r="AN79" s="4">
+        <v>1.4935907398805501E-2</v>
+      </c>
+      <c r="AO79" s="4">
+        <v>0.89154600077571156</v>
+      </c>
+      <c r="AP79" s="4">
+        <v>1.4935907398805501E-2</v>
+      </c>
+      <c r="AQ79" s="4">
+        <v>1.4935907398805501E-2</v>
+      </c>
+      <c r="AR79" s="4">
+        <v>0.89154600077571156</v>
+      </c>
+      <c r="AS79" s="4">
+        <v>0.13680377698261501</v>
+      </c>
+      <c r="AT79" s="4">
+        <v>6.6276974950442999E-3</v>
+      </c>
+      <c r="AU79" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV79" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW79" s="4">
+        <v>1.4935907398805501E-2</v>
+      </c>
+      <c r="AX79" s="4">
+        <v>0.89154600077571156</v>
+      </c>
+      <c r="AY79" s="4">
+        <v>1.4935907398805501E-2</v>
+      </c>
+      <c r="AZ79" s="4">
+        <v>1.4935907398805501E-2</v>
+      </c>
+      <c r="BA79" s="4">
+        <v>0.89154600077571156</v>
+      </c>
+      <c r="BB79" s="4">
+        <v>0.13680377698261501</v>
+      </c>
+      <c r="BC79" s="4">
+        <v>6.6276974950442999E-3</v>
+      </c>
+      <c r="BD79" s="4"/>
+      <c r="BE79" s="4"/>
+      <c r="BF79" s="4"/>
+      <c r="BG79" s="4"/>
+      <c r="BH79" s="4"/>
+      <c r="BI79" s="4"/>
+      <c r="BJ79" s="4"/>
+      <c r="BK79" s="4"/>
+      <c r="BL79" s="4"/>
+      <c r="BM79" s="4"/>
+      <c r="BN79" s="4"/>
+      <c r="BO79" s="4"/>
+      <c r="BP79" s="4"/>
+      <c r="BQ79" s="4"/>
+      <c r="BR79" s="4"/>
+      <c r="BS79" s="4"/>
+      <c r="BT79" s="4"/>
+      <c r="BU79" s="4"/>
+      <c r="BV79" s="4"/>
+      <c r="BW79" s="4"/>
+      <c r="BX79" s="4"/>
+    </row>
+    <row r="80" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A80" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C80" s="4">
+        <v>8</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F80" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G80" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J80" s="4">
+        <v>5</v>
+      </c>
+      <c r="K80" s="4">
+        <v>5</v>
+      </c>
+      <c r="L80" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M80" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N80" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O80" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P80" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q80" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R80" s="4">
+        <v>1</v>
+      </c>
+      <c r="S80" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T80" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U80" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V80" s="4">
+        <v>5</v>
+      </c>
+      <c r="W80" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X80" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z80" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA80" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB80" s="4"/>
+      <c r="AC80" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD80" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE80" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF80" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG80" s="4">
+        <v>80</v>
+      </c>
+      <c r="AH80" s="4">
+        <v>50</v>
+      </c>
+      <c r="AI80" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ80" s="4">
+        <v>6.5384725709254396E-2</v>
+      </c>
+      <c r="AK80" s="4">
+        <v>1.47605000851971E-2</v>
+      </c>
+      <c r="AL80" s="4">
+        <v>0.80096396224472111</v>
+      </c>
+      <c r="AM80" s="4">
+        <v>-0.104392051504808</v>
+      </c>
+      <c r="AN80" s="4">
+        <v>3.0052698304400799E-2</v>
+      </c>
+      <c r="AO80" s="4">
+        <v>0.78177855341725544</v>
+      </c>
+      <c r="AP80" s="4">
+        <v>3.0052698304400799E-2</v>
+      </c>
+      <c r="AQ80" s="4">
+        <v>3.0052698304400799E-2</v>
+      </c>
+      <c r="AR80" s="4">
+        <v>0.78177855341725544</v>
+      </c>
+      <c r="AS80" s="4">
+        <v>0.14650355272833609</v>
+      </c>
+      <c r="AT80" s="4">
+        <v>-6.3805215826736095E-2</v>
+      </c>
+      <c r="AU80" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV80" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW80" s="4">
+        <v>3.0052698304400799E-2</v>
+      </c>
+      <c r="AX80" s="4">
+        <v>0.78177855341725544</v>
+      </c>
+      <c r="AY80" s="4">
+        <v>3.0052698304400799E-2</v>
+      </c>
+      <c r="AZ80" s="4">
+        <v>3.0052698304400799E-2</v>
+      </c>
+      <c r="BA80" s="4">
+        <v>0.78177855341725544</v>
+      </c>
+      <c r="BB80" s="4">
+        <v>0.14650355272833609</v>
+      </c>
+      <c r="BC80" s="4">
+        <v>-6.3805215826736095E-2</v>
+      </c>
+      <c r="BD80" s="4"/>
+      <c r="BE80" s="4"/>
+      <c r="BF80" s="4"/>
+      <c r="BG80" s="4"/>
+      <c r="BH80" s="4"/>
+      <c r="BI80" s="4"/>
+      <c r="BJ80" s="4"/>
+      <c r="BK80" s="4"/>
+      <c r="BL80" s="4"/>
+      <c r="BM80" s="4"/>
+      <c r="BN80" s="4"/>
+      <c r="BO80" s="4"/>
+      <c r="BP80" s="4"/>
+      <c r="BQ80" s="4"/>
+      <c r="BR80" s="4"/>
+      <c r="BS80" s="4"/>
+      <c r="BT80" s="4"/>
+      <c r="BU80" s="4"/>
+      <c r="BV80" s="4"/>
+      <c r="BW80" s="4"/>
+      <c r="BX80" s="4"/>
+    </row>
+    <row r="81" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A81" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="C81" s="4">
+        <v>9</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F81" s="4">
+        <v>16590</v>
+      </c>
+      <c r="G81" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J81" s="4">
+        <v>5</v>
+      </c>
+      <c r="K81" s="4">
+        <v>5</v>
+      </c>
+      <c r="L81" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M81" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N81" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O81" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P81" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q81" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="R81" s="4">
+        <v>1</v>
+      </c>
+      <c r="S81" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T81" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="U81" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="V81" s="4">
+        <v>5</v>
+      </c>
+      <c r="W81" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="X81" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z81" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AA81" s="4">
+        <v>4000</v>
+      </c>
+      <c r="AB81" s="4"/>
+      <c r="AC81" s="4">
+        <v>256</v>
+      </c>
+      <c r="AD81" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE81" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="AF81" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG81" s="4">
+        <v>80</v>
+      </c>
+      <c r="AH81" s="4">
+        <v>50</v>
+      </c>
+      <c r="AI81" s="4">
+        <v>30</v>
+      </c>
+      <c r="AJ81" s="4">
+        <v>5.0636944282373302E-2</v>
+      </c>
+      <c r="AK81" s="4">
+        <v>7.4605903211662E-3</v>
+      </c>
+      <c r="AL81" s="4">
+        <v>0.89939864311714668</v>
+      </c>
+      <c r="AM81" s="4">
+        <v>-1.414778424593947</v>
+      </c>
+      <c r="AN81" s="4">
+        <v>1.7238138797533199E-2</v>
+      </c>
+      <c r="AO81" s="4">
+        <v>0.87482882413121021</v>
+      </c>
+      <c r="AP81" s="4">
+        <v>1.7238138797533199E-2</v>
+      </c>
+      <c r="AQ81" s="4">
+        <v>1.7238138797533199E-2</v>
+      </c>
+      <c r="AR81" s="4">
+        <v>0.87482882413121021</v>
+      </c>
+      <c r="AS81" s="4">
+        <v>0.2392214679904649</v>
+      </c>
+      <c r="AT81" s="4">
+        <v>-0.73705716104974472</v>
+      </c>
+      <c r="AU81" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="AV81" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW81" s="4">
+        <v>1.7238138797533199E-2</v>
+      </c>
+      <c r="AX81" s="4">
+        <v>0.87482882413121021</v>
+      </c>
+      <c r="AY81" s="4">
+        <v>1.7238138797533199E-2</v>
+      </c>
+      <c r="AZ81" s="4">
+        <v>1.7238138797533199E-2</v>
+      </c>
+      <c r="BA81" s="4">
+        <v>0.87482882413121021</v>
+      </c>
+      <c r="BB81" s="4">
+        <v>0.2392214679904649</v>
+      </c>
+      <c r="BC81" s="4">
+        <v>-0.73705716104974472</v>
+      </c>
+      <c r="BD81" s="4"/>
+      <c r="BE81" s="4"/>
+      <c r="BF81" s="4"/>
+      <c r="BG81" s="4"/>
+      <c r="BH81" s="4"/>
+      <c r="BI81" s="4"/>
+      <c r="BJ81" s="4"/>
+      <c r="BK81" s="4"/>
+      <c r="BL81" s="4"/>
+      <c r="BM81" s="4"/>
+      <c r="BN81" s="4"/>
+      <c r="BO81" s="4"/>
+      <c r="BP81" s="4"/>
+      <c r="BQ81" s="4"/>
+      <c r="BR81" s="4"/>
+      <c r="BS81" s="4"/>
+      <c r="BT81" s="4"/>
+      <c r="BU81" s="4"/>
+      <c r="BV81" s="4"/>
+      <c r="BW81" s="4"/>
+      <c r="BX81" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13951,111 +22244,208 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0540E48-251D-4D09-8CD4-032BFADB5AE7}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B3" t="s">
         <v>190</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C3" t="s">
         <v>191</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D3" t="s">
         <v>189</v>
       </c>
+      <c r="F3" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G3" t="s">
+        <v>190</v>
+      </c>
+      <c r="H3" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B2">
+      <c r="B4" s="5">
         <v>0.97048192468175909</v>
       </c>
-      <c r="C2">
+      <c r="C4" s="5">
         <v>-2.9513877379236675</v>
       </c>
-      <c r="D2">
+      <c r="D4" s="5">
         <v>10</v>
       </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0.97044952650866578</v>
+      </c>
+      <c r="H4" s="5">
+        <v>-2.9691585786175829</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0.97044952650866578</v>
+      </c>
+      <c r="C5" s="5">
+        <v>-2.9691585786175834</v>
+      </c>
+      <c r="D5" s="5">
+        <v>10</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0.97044952650866578</v>
+      </c>
+      <c r="H5" s="5">
+        <v>-2.9691585786175829</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B3">
+      <c r="B6" s="5">
         <v>0.96071318619906665</v>
       </c>
-      <c r="C3">
+      <c r="C6" s="5">
         <v>-3.3906497875796133</v>
       </c>
-      <c r="D3">
+      <c r="D6" s="5">
         <v>10</v>
       </c>
+      <c r="F6" s="3">
+        <v>3</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0.87715248869311213</v>
+      </c>
+      <c r="H6" s="5">
+        <v>-0.98986312472231286</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B4">
+      <c r="B7" s="5">
         <v>0.95422737704073002</v>
       </c>
-      <c r="C4">
+      <c r="C7" s="5">
         <v>-2.2058750102601712</v>
       </c>
-      <c r="D4">
+      <c r="D7" s="5">
         <v>10</v>
       </c>
+      <c r="F7" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0.87715248869311213</v>
+      </c>
+      <c r="H7" s="5">
+        <v>-0.98986312472231286</v>
+      </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B5">
+      <c r="B8" s="5">
         <v>0.93661639560311849</v>
       </c>
-      <c r="C5">
+      <c r="C8" s="5">
         <v>-0.69562538852536537</v>
       </c>
-      <c r="D5">
+      <c r="D8" s="5">
         <v>10</v>
       </c>
+      <c r="F8" s="3">
+        <v>5</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0.84763564571046746</v>
+      </c>
+      <c r="H8" s="5">
+        <v>-0.23567428531219892</v>
+      </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B6">
+      <c r="B9" s="5">
         <v>0.93174974586977211</v>
       </c>
-      <c r="C6">
+      <c r="C9" s="5">
         <v>-5.8401369475180397E-2</v>
       </c>
-      <c r="D6">
+      <c r="D9" s="5">
         <v>10</v>
       </c>
+      <c r="F9" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0.84763564571046746</v>
+      </c>
+      <c r="H9" s="5">
+        <v>-0.23567428531219892</v>
+      </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B7">
-        <v>0.95075772587888907</v>
-      </c>
-      <c r="C7">
-        <v>-1.8603878587527996</v>
-      </c>
-      <c r="D7">
-        <v>50</v>
+      <c r="B10" s="5">
+        <v>0.95403969265051847</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-2.0451829787302636</v>
+      </c>
+      <c r="D10" s="5">
+        <v>60</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0.89841255363741512</v>
+      </c>
+      <c r="H10" s="5">
+        <v>-1.3982319962173648</v>
       </c>
     </row>
   </sheetData>
